--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_36.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2212823.449348561</v>
+        <v>2213894.573060837</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14697842.82031947</v>
+        <v>14697842.82031952</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14697842.82031947</v>
+        <v>14697842.82031952</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984940458</v>
+        <v>657188.6984940564</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984940458</v>
+        <v>657188.6984940564</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30280594.1082212</v>
+        <v>30280594.10822119</v>
       </c>
     </row>
   </sheetData>
@@ -739,22 +739,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>139.4144593584064</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>128.9709564352693</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
         <v>133.6519859716245</v>
@@ -988,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>158.1721839527247</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S6" t="n">
-        <v>374</v>
+        <v>160.3860621832915</v>
       </c>
       <c r="T6" t="n">
-        <v>374</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U6" t="n">
         <v>0.1959257979225981</v>
@@ -1036,10 +1036,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>326.5695244157589</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -1216,10 +1216,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>128.9709564352694</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1419,7 +1419,7 @@
         <v>142.2280170485541</v>
       </c>
       <c r="T11" t="n">
-        <v>261.2171194170061</v>
+        <v>260.5210344205111</v>
       </c>
       <c r="U11" t="n">
         <v>330.1032663978569</v>
@@ -1428,7 +1428,7 @@
         <v>310.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>318.6773909844526</v>
+        <v>319.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>273.2818334606677</v>
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>42.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>23.67209722191262</v>
@@ -1459,13 +1459,13 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>228.8924124088876</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H12" t="n">
         <v>324.5441815260438</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1489,13 +1489,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>32.99466045383283</v>
       </c>
       <c r="R12" t="n">
         <v>179.2619859716246</v>
       </c>
       <c r="S12" t="n">
-        <v>132.901311285366</v>
+        <v>451.901311285366</v>
       </c>
       <c r="T12" t="n">
         <v>83.17594446279683</v>
@@ -1504,7 +1504,7 @@
         <v>81.1584257979226</v>
       </c>
       <c r="V12" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W12" t="n">
         <v>113.3731429098285</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3.305168319656873</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M13" t="n">
         <v>97.89093927140236</v>
@@ -1568,7 +1568,7 @@
         <v>288.4057989676218</v>
       </c>
       <c r="Q13" t="n">
-        <v>351.422266425598</v>
+        <v>348.5719049481316</v>
       </c>
       <c r="R13" t="n">
         <v>377.845046013938</v>
@@ -1617,7 +1617,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H14" t="n">
         <v>73.89995518593946</v>
@@ -1671,7 +1671,7 @@
         <v>273.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>192.3174326828064</v>
+        <v>191.6213476863115</v>
       </c>
     </row>
     <row r="15">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C15" t="n">
         <v>42.09991244551929</v>
@@ -1693,7 +1693,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G15" t="n">
         <v>5.950139648612264</v>
@@ -1729,16 +1729,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>179.2619859716245</v>
+        <v>402.2042587319001</v>
       </c>
       <c r="S15" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T15" t="n">
-        <v>83.17594446279685</v>
+        <v>402.1759444627968</v>
       </c>
       <c r="U15" t="n">
-        <v>81.15842579792258</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V15" t="n">
         <v>95.51066719152016</v>
@@ -1750,7 +1750,7 @@
         <v>100.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>303.3336655264099</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1854,7 +1854,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>83.28199540259408</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H17" t="n">
         <v>73.89995518593946</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T17" t="n">
         <v>261.2171194170061</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>288.4988294066021</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
         <v>361.0999124455193</v>
@@ -1927,7 +1927,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F18" t="n">
         <v>20.63624233787687</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>179.2619859716245</v>
+        <v>402.2042587319001</v>
       </c>
       <c r="S18" t="n">
         <v>132.901311285366</v>
@@ -2079,7 +2079,7 @@
         <v>162.9993129555745</v>
       </c>
       <c r="C20" t="n">
-        <v>130.4745782429939</v>
+        <v>129.778493246499</v>
       </c>
       <c r="D20" t="n">
         <v>91.33915573984979</v>
@@ -2091,10 +2091,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>83.28199540259408</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H20" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T20" t="n">
         <v>261.2171194170061</v>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C21" t="n">
         <v>42.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>246.6143699821882</v>
       </c>
       <c r="F21" t="n">
-        <v>243.5785150981523</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>5.950139648612264</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H21" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,22 +2203,22 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S21" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T21" t="n">
-        <v>83.17594446279685</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U21" t="n">
-        <v>81.15842579792258</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V21" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
         <v>100.8627394453875</v>
@@ -2264,16 +2264,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M22" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N22" t="n">
         <v>150.9111244520127</v>
       </c>
       <c r="O22" t="n">
-        <v>225.052317355647</v>
+        <v>227.9026788331133</v>
       </c>
       <c r="P22" t="n">
         <v>288.4057989676218</v>
@@ -2282,10 +2282,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S22" t="n">
-        <v>31.84005347334727</v>
+        <v>28.98969199588089</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H23" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520589</v>
       </c>
       <c r="T23" t="n">
         <v>261.2171194170061</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>65.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
         <v>28.93768689770263</v>
@@ -2407,13 +2407,13 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H24" t="n">
-        <v>324.5441815260438</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I24" t="n">
-        <v>150.6287435188524</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2437,31 +2437,31 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S24" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T24" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W24" t="n">
         <v>113.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>100.8627394453875</v>
+        <v>323.805012205663</v>
       </c>
       <c r="Y24" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2501,10 +2501,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M25" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N25" t="n">
         <v>150.9111244520127</v>
@@ -2519,10 +2519,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S25" t="n">
-        <v>28.98969199588089</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>82.58591040612572</v>
+        <v>82.58591040612345</v>
       </c>
       <c r="H26" t="n">
         <v>73.89995518593948</v>
@@ -2629,16 +2629,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>288.4988294066021</v>
       </c>
       <c r="C27" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>251.8799596579781</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>339.6362423378769</v>
@@ -2756,10 +2756,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.845046013938</v>
+        <v>374.994684536472</v>
       </c>
       <c r="S28" t="n">
-        <v>28.98969199588131</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040612345</v>
       </c>
       <c r="H29" t="n">
         <v>73.89995518593948</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>141.5319320521043</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T29" t="n">
         <v>261.2171194170061</v>
@@ -2872,22 +2872,22 @@
         <v>42.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>5.950139648612248</v>
+        <v>38.9448001024447</v>
       </c>
       <c r="H30" t="n">
-        <v>228.4864542863195</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>81.1584257979226</v>
       </c>
       <c r="V30" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>100.8627394453875</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>6.155529797123435</v>
+        <v>3.305168319657323</v>
       </c>
       <c r="M31" t="n">
-        <v>95.04057779393607</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N31" t="n">
         <v>150.9111244520127</v>
@@ -3042,7 +3042,7 @@
         <v>83.28199540259408</v>
       </c>
       <c r="H32" t="n">
-        <v>73.89995518593946</v>
+        <v>73.20387018954538</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>-6.971158976935874e-11</v>
       </c>
       <c r="S32" t="n">
         <v>142.2280170485541</v>
@@ -3081,7 +3081,7 @@
         <v>261.2171194170061</v>
       </c>
       <c r="U32" t="n">
-        <v>329.4071814014073</v>
+        <v>330.1032663978569</v>
       </c>
       <c r="V32" t="n">
         <v>310.8510241668239</v>
@@ -3103,28 +3103,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65.55655664632661</v>
+        <v>98.55121710015912</v>
       </c>
       <c r="C33" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
         <v>20.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>156.5788831674647</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H33" t="n">
         <v>5.544181526043758</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>179.2619859716245</v>
@@ -3160,10 +3160,10 @@
         <v>83.17594446279685</v>
       </c>
       <c r="U33" t="n">
-        <v>400.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V33" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W33" t="n">
         <v>113.3731429098285</v>
@@ -3172,7 +3172,7 @@
         <v>100.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -3233,7 +3233,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S34" t="n">
-        <v>28.98969199589262</v>
+        <v>28.9896919958863</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3270,10 +3270,10 @@
         <v>13.33915573984979</v>
       </c>
       <c r="E35" t="n">
-        <v>7.363289606868648</v>
+        <v>4.062359796337299</v>
       </c>
       <c r="F35" t="n">
-        <v>4.588698897501682</v>
+        <v>7.889628708011855</v>
       </c>
       <c r="G35" t="n">
         <v>5.2819954025941</v>
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>374.0000000000346</v>
+        <v>374.0000000000437</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>283.736065417468</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3358,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>200.9138413876248</v>
       </c>
       <c r="I36" t="n">
         <v>189.9476123064429</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R36" t="n">
         <v>101.2619859716246</v>
@@ -3409,7 +3409,7 @@
         <v>22.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.391392766134345</v>
+        <v>374.0000000000437</v>
       </c>
     </row>
     <row r="37">
@@ -3510,10 +3510,10 @@
         <v>7.363289606868648</v>
       </c>
       <c r="F38" t="n">
-        <v>4.588698897501682</v>
+        <v>4.58869889748053</v>
       </c>
       <c r="G38" t="n">
-        <v>5.2819954025941</v>
+        <v>5.281995402594077</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>64.22801704855405</v>
+        <v>64.22801704855408</v>
       </c>
       <c r="T38" t="n">
         <v>183.2171194170061</v>
@@ -3580,13 +3580,13 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>106.2240344705499</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -3622,19 +3622,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>101.2619859716246</v>
+        <v>101.2619859716245</v>
       </c>
       <c r="S39" t="n">
-        <v>54.90131128536602</v>
+        <v>54.90131128536603</v>
       </c>
       <c r="T39" t="n">
-        <v>5.175944462796835</v>
+        <v>5.175944462796849</v>
       </c>
       <c r="U39" t="n">
-        <v>3.158425797922597</v>
+        <v>3.158425797922575</v>
       </c>
       <c r="V39" t="n">
         <v>17.51066719152016</v>
@@ -3643,7 +3643,7 @@
         <v>35.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>22.86273944538755</v>
+        <v>182.9724879337324</v>
       </c>
       <c r="Y39" t="n">
         <v>2.391392766134345</v>
@@ -3689,10 +3689,10 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>19.89093927140236</v>
+        <v>19.89093927140237</v>
       </c>
       <c r="N40" t="n">
-        <v>72.91112445201273</v>
+        <v>72.9111244520127</v>
       </c>
       <c r="O40" t="n">
         <v>149.9026788331133</v>
@@ -3704,7 +3704,7 @@
         <v>273.422266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>299.845046013938</v>
+        <v>299.8450460139379</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>14.46772992602491</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T41" t="n">
-        <v>113.8095999937492</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U41" t="n">
-        <v>356.1032663978569</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>336.8510241668239</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>91.55655664632661</v>
+        <v>93.94333009177598</v>
       </c>
       <c r="C42" t="n">
         <v>68.09991244551929</v>
@@ -3826,13 +3826,13 @@
         <v>49.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>49.02301578334749</v>
+        <v>46.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>31.95013964861225</v>
+        <v>31.95013964861226</v>
       </c>
       <c r="H42" t="n">
-        <v>31.54418152604377</v>
+        <v>31.54418152604376</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>205.2619859716246</v>
+        <v>205.2619859716245</v>
       </c>
       <c r="S42" t="n">
         <v>158.901311285366</v>
@@ -3929,22 +3929,22 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>62.05874345008469</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>253.9026788331133</v>
+        <v>59.39567678885051</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>374.0000000000728</v>
+        <v>374.0000000001092</v>
       </c>
       <c r="R43" t="n">
-        <v>374.0000000000728</v>
+        <v>374.0000000001092</v>
       </c>
       <c r="S43" t="n">
-        <v>57.84005347334724</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>125.8743140373897</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -3984,10 +3984,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>109.2819954025941</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4023,25 +4023,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>287.2171194170061</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>345.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>299.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>130.1471299822641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4069,7 +4069,7 @@
         <v>31.95013964861225</v>
       </c>
       <c r="H45" t="n">
-        <v>31.54418152604377</v>
+        <v>33.93095497149323</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.386773445470614</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>205.2619859716246</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>32.15552979712344</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>123.8909392714024</v>
@@ -4175,10 +4175,10 @@
         <v>314.4057989676218</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>194.8508807591932</v>
       </c>
       <c r="R46" t="n">
-        <v>162.6953509620699</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>57.84005347334724</v>
@@ -4321,19 +4321,19 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L2" t="n">
-        <v>145.6202453266332</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M2" t="n">
-        <v>385.22</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="N2" t="n">
-        <v>385.22</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="O2" t="n">
         <v>755.48</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1095.466996464934</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="C3" t="n">
-        <v>730.7196101563284</v>
+        <v>714.4543850996074</v>
       </c>
       <c r="D3" t="n">
-        <v>379.2674011687499</v>
+        <v>714.4543850996074</v>
       </c>
       <c r="E3" t="n">
-        <v>33.13396963146437</v>
+        <v>714.4543850996074</v>
       </c>
       <c r="F3" t="n">
-        <v>33.13396963146437</v>
+        <v>573.6316988789948</v>
       </c>
       <c r="G3" t="n">
-        <v>33.13396963146437</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="H3" t="n">
-        <v>33.13396963146437</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="I3" t="n">
         <v>33.13396963146437</v>
@@ -4421,31 +4421,31 @@
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1365.726306631041</v>
+        <v>1349.46108157432</v>
       </c>
       <c r="R3" t="n">
-        <v>1230.724300599097</v>
+        <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>1167.604289199738</v>
+        <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>1163.085658429236</v>
+        <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>1162.887753582849</v>
+        <v>1146.622528526128</v>
       </c>
       <c r="V3" t="n">
-        <v>1148.230513995455</v>
+        <v>1131.965288938734</v>
       </c>
       <c r="W3" t="n">
-        <v>1115.530369642093</v>
+        <v>1099.265144585372</v>
       </c>
       <c r="X3" t="n">
-        <v>1095.466996464934</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="Y3" t="n">
-        <v>1095.466996464934</v>
+        <v>1079.201771408213</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>724.8179593327073</v>
+        <v>494.7030048740901</v>
       </c>
       <c r="C4" t="n">
-        <v>724.8179593327073</v>
+        <v>620.7050106925259</v>
       </c>
       <c r="D4" t="n">
-        <v>838.1371034577074</v>
+        <v>620.7050106925259</v>
       </c>
       <c r="E4" t="n">
-        <v>955.9660076691205</v>
+        <v>738.5339149039389</v>
       </c>
       <c r="F4" t="n">
-        <v>1080.326980261056</v>
+        <v>862.8948874958744</v>
       </c>
       <c r="G4" t="n">
-        <v>1080.326980261056</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="H4" t="n">
-        <v>1251.462556240126</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="I4" t="n">
-        <v>1251.462556240126</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
         <v>1386.743548464727</v>
@@ -4509,22 +4509,22 @@
         <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>194.9566152966946</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="U4" t="n">
-        <v>441.5177403939977</v>
+        <v>232.2629131708643</v>
       </c>
       <c r="V4" t="n">
-        <v>441.5177403939977</v>
+        <v>232.2629131708643</v>
       </c>
       <c r="W4" t="n">
-        <v>613.408658653675</v>
+        <v>232.2629131708643</v>
       </c>
       <c r="X4" t="n">
-        <v>613.408658653675</v>
+        <v>383.2937041950578</v>
       </c>
       <c r="Y4" t="n">
-        <v>724.8179593327073</v>
+        <v>494.7030048740901</v>
       </c>
     </row>
     <row r="5">
@@ -4561,22 +4561,22 @@
         <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>770.4399999999999</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L5" t="n">
-        <v>834.5019149748742</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M5" t="n">
-        <v>1204.761914974874</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.908108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1314.492137192891</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>363.3030116424684</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="C6" t="n">
-        <v>363.3030116424684</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="D6" t="n">
-        <v>363.3030116424684</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="E6" t="n">
-        <v>363.3030116424684</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="F6" t="n">
-        <v>363.3030116424684</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="G6" t="n">
-        <v>363.3030116424684</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4661,28 +4661,28 @@
         <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1186.477229162326</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>808.6994513845481</v>
+        <v>1049.238982493446</v>
       </c>
       <c r="T6" t="n">
-        <v>430.9216736067702</v>
+        <v>1044.720351722944</v>
       </c>
       <c r="U6" t="n">
-        <v>430.7237687603838</v>
+        <v>1044.522446876557</v>
       </c>
       <c r="V6" t="n">
-        <v>416.0665291729897</v>
+        <v>1029.865207289163</v>
       </c>
       <c r="W6" t="n">
-        <v>383.3663848196276</v>
+        <v>997.165062935801</v>
       </c>
       <c r="X6" t="n">
-        <v>363.3030116424684</v>
+        <v>619.3872851580231</v>
       </c>
       <c r="Y6" t="n">
-        <v>363.3030116424684</v>
+        <v>241.6095073802453</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>218.6183178716313</v>
+        <v>404.1174293695179</v>
       </c>
       <c r="C7" t="n">
-        <v>344.620323690067</v>
+        <v>530.1194351879536</v>
       </c>
       <c r="D7" t="n">
-        <v>457.9394678150671</v>
+        <v>643.4385793129537</v>
       </c>
       <c r="E7" t="n">
-        <v>575.7683720264802</v>
+        <v>761.2674835243668</v>
       </c>
       <c r="F7" t="n">
-        <v>700.1293446184156</v>
+        <v>885.6284561163022</v>
       </c>
       <c r="G7" t="n">
-        <v>853.7180055872682</v>
+        <v>1039.217117085155</v>
       </c>
       <c r="H7" t="n">
-        <v>1024.853581566338</v>
+        <v>1210.352693064224</v>
       </c>
       <c r="I7" t="n">
-        <v>1251.462556240126</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4758,10 +4758,10 @@
         <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>29.92</v>
+        <v>180.9507910241935</v>
       </c>
       <c r="Y7" t="n">
-        <v>106.8609802053391</v>
+        <v>292.3600917032257</v>
       </c>
     </row>
     <row r="8">
@@ -4795,25 +4795,25 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K8" t="n">
-        <v>770.4399999999999</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L8" t="n">
-        <v>834.5019149748742</v>
+        <v>327.128108133742</v>
       </c>
       <c r="M8" t="n">
-        <v>1204.761914974874</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>1204.761914974874</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>1204.761914974874</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P8" t="n">
-        <v>1262.853806841132</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1222.526720202428</v>
+        <v>746.1195952961839</v>
       </c>
       <c r="C9" t="n">
-        <v>857.7793338938229</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="D9" t="n">
-        <v>506.3271249062445</v>
+        <v>29.92</v>
       </c>
       <c r="E9" t="n">
-        <v>160.193693368959</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1357.784024336592</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.664012937232</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T9" t="n">
-        <v>1290.14538216673</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U9" t="n">
-        <v>1289.947477320344</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V9" t="n">
-        <v>1275.29023773295</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W9" t="n">
-        <v>1242.590093379587</v>
+        <v>1096.051174953908</v>
       </c>
       <c r="X9" t="n">
-        <v>1222.526720202428</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y9" t="n">
-        <v>1222.526720202428</v>
+        <v>1075.987801776748</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>879.9559519984875</v>
+        <v>965.2449940752859</v>
       </c>
       <c r="C10" t="n">
-        <v>1005.957957816923</v>
+        <v>1091.246999893722</v>
       </c>
       <c r="D10" t="n">
-        <v>1024.853581566338</v>
+        <v>1091.246999893722</v>
       </c>
       <c r="E10" t="n">
-        <v>1024.853581566338</v>
+        <v>1091.246999893722</v>
       </c>
       <c r="F10" t="n">
-        <v>1024.853581566338</v>
+        <v>1215.607972485657</v>
       </c>
       <c r="G10" t="n">
-        <v>1024.853581566338</v>
+        <v>1215.607972485657</v>
       </c>
       <c r="H10" t="n">
-        <v>1024.853581566338</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="I10" t="n">
-        <v>1251.462556240126</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4989,16 +4989,16 @@
         <v>505.7585226289696</v>
       </c>
       <c r="V10" t="n">
-        <v>505.7585226289696</v>
+        <v>642.3232847914151</v>
       </c>
       <c r="W10" t="n">
-        <v>505.7585226289696</v>
+        <v>814.2142030510925</v>
       </c>
       <c r="X10" t="n">
-        <v>656.789313653163</v>
+        <v>965.2449940752859</v>
       </c>
       <c r="Y10" t="n">
-        <v>768.1986143321953</v>
+        <v>965.2449940752859</v>
       </c>
     </row>
     <row r="11">
@@ -5041,7 +5041,7 @@
         <v>1446.624956504992</v>
       </c>
       <c r="M11" t="n">
-        <v>2095.074956504992</v>
+        <v>1585.241587554807</v>
       </c>
       <c r="N11" t="n">
         <v>2233.691587554807</v>
@@ -5062,13 +5062,13 @@
         <v>2476.335336314592</v>
       </c>
       <c r="T11" t="n">
-        <v>2212.479660135798</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U11" t="n">
-        <v>1879.04201730968</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V11" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W11" t="n">
         <v>1243.154729278087</v>
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>727.9379119575181</v>
+        <v>1016.832194327384</v>
       </c>
       <c r="C12" t="n">
-        <v>685.4127478711349</v>
+        <v>974.307030241001</v>
       </c>
       <c r="D12" t="n">
-        <v>656.1827611057787</v>
+        <v>622.8548212534226</v>
       </c>
       <c r="E12" t="n">
-        <v>632.2715517907154</v>
+        <v>598.9436119383594</v>
       </c>
       <c r="F12" t="n">
-        <v>611.4268625605367</v>
+        <v>578.0989227081807</v>
       </c>
       <c r="G12" t="n">
-        <v>380.2224055818624</v>
+        <v>572.0886806388754</v>
       </c>
       <c r="H12" t="n">
-        <v>52.4</v>
+        <v>244.266275057013</v>
       </c>
       <c r="I12" t="n">
         <v>52.4</v>
@@ -5132,31 +5132,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2313.990605368536</v>
+        <v>2280.662665516179</v>
       </c>
       <c r="R12" t="n">
-        <v>2132.917892265885</v>
+        <v>2099.589952413528</v>
       </c>
       <c r="S12" t="n">
-        <v>1998.674143492788</v>
+        <v>1643.123981418209</v>
       </c>
       <c r="T12" t="n">
-        <v>1914.658037974811</v>
+        <v>1559.107875900233</v>
       </c>
       <c r="U12" t="n">
-        <v>1832.679830098122</v>
+        <v>1477.129668023543</v>
       </c>
       <c r="V12" t="n">
-        <v>1413.982186470323</v>
+        <v>1380.654246617967</v>
       </c>
       <c r="W12" t="n">
-        <v>1299.463860298779</v>
+        <v>1266.135920446423</v>
       </c>
       <c r="X12" t="n">
-        <v>1197.582305303438</v>
+        <v>1164.254365451082</v>
       </c>
       <c r="Y12" t="n">
-        <v>1116.378878266939</v>
+        <v>1083.050938414583</v>
       </c>
     </row>
     <row r="13">
@@ -5196,19 +5196,19 @@
         <v>1597.372803794637</v>
       </c>
       <c r="L13" t="n">
-        <v>1594.034249936398</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M13" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N13" t="n">
-        <v>1342.71903405416</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O13" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P13" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q13" t="n">
         <v>466.2233328154397</v>
@@ -5245,19 +5245,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>607.5035534240029</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C14" t="n">
-        <v>475.7110501482515</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D14" t="n">
-        <v>383.4492766736557</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E14" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F14" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G14" t="n">
         <v>127.0464193797368</v>
@@ -5272,22 +5272,22 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K14" t="n">
-        <v>790.1259849731395</v>
+        <v>517.0148001162504</v>
       </c>
       <c r="L14" t="n">
-        <v>1020.623267284697</v>
+        <v>1165.46480011625</v>
       </c>
       <c r="M14" t="n">
-        <v>1669.073267284698</v>
+        <v>1165.46480011625</v>
       </c>
       <c r="N14" t="n">
-        <v>2233.691587554807</v>
+        <v>1165.46480011625</v>
       </c>
       <c r="O14" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P14" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q14" t="n">
         <v>2620</v>
@@ -5314,7 +5314,7 @@
         <v>966.4093570991351</v>
       </c>
       <c r="Y14" t="n">
-        <v>772.1493240861994</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="15">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>824.9659192703713</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C15" t="n">
-        <v>782.4407551839881</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D15" t="n">
-        <v>753.2107684186319</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E15" t="n">
-        <v>407.0773368813464</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F15" t="n">
         <v>64.01042542894548</v>
@@ -5372,28 +5372,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2132.917892265885</v>
+        <v>1907.723677356516</v>
       </c>
       <c r="S15" t="n">
-        <v>1998.674143492788</v>
+        <v>1773.479928583419</v>
       </c>
       <c r="T15" t="n">
-        <v>1914.658037974811</v>
+        <v>1367.24160084322</v>
       </c>
       <c r="U15" t="n">
-        <v>1832.679830098122</v>
+        <v>963.0411707443078</v>
       </c>
       <c r="V15" t="n">
-        <v>1736.204408692546</v>
+        <v>866.5657493387318</v>
       </c>
       <c r="W15" t="n">
-        <v>1621.686082521002</v>
+        <v>752.0474231671878</v>
       </c>
       <c r="X15" t="n">
-        <v>1519.804527525661</v>
+        <v>650.1658681718469</v>
       </c>
       <c r="Y15" t="n">
-        <v>1213.406885579792</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="16">
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C17" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D17" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E17" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F17" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G17" t="n">
         <v>127.0464193797368</v>
@@ -5509,13 +5509,13 @@
         <v>567.6776741934345</v>
       </c>
       <c r="K17" t="n">
-        <v>753.4744118316256</v>
+        <v>1216.127674193434</v>
       </c>
       <c r="L17" t="n">
-        <v>983.9716941431833</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="M17" t="n">
-        <v>1632.421694143184</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="N17" t="n">
         <v>1637.361628029778</v>
@@ -5533,25 +5533,25 @@
         <v>2620</v>
       </c>
       <c r="S17" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T17" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U17" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V17" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W17" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X17" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y17" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="18">
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1147.188141492594</v>
+        <v>824.9659192703712</v>
       </c>
       <c r="C18" t="n">
-        <v>782.4407551839881</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D18" t="n">
-        <v>430.9885461964096</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E18" t="n">
         <v>84.85511465912413</v>
@@ -5609,28 +5609,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R18" t="n">
-        <v>2132.917892265885</v>
+        <v>1907.723677356516</v>
       </c>
       <c r="S18" t="n">
-        <v>1998.674143492788</v>
+        <v>1773.479928583419</v>
       </c>
       <c r="T18" t="n">
-        <v>1914.658037974811</v>
+        <v>1689.463823065442</v>
       </c>
       <c r="U18" t="n">
-        <v>1832.679830098122</v>
+        <v>1607.485615188752</v>
       </c>
       <c r="V18" t="n">
-        <v>1736.204408692546</v>
+        <v>1511.010193783176</v>
       </c>
       <c r="W18" t="n">
-        <v>1621.686082521002</v>
+        <v>1396.491867611632</v>
       </c>
       <c r="X18" t="n">
-        <v>1519.804527525661</v>
+        <v>1294.610312616291</v>
       </c>
       <c r="Y18" t="n">
-        <v>1438.601100489161</v>
+        <v>1213.406885579792</v>
       </c>
     </row>
     <row r="19">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C20" t="n">
         <v>476.4141663063272</v>
@@ -5743,52 +5743,52 @@
         <v>52.4</v>
       </c>
       <c r="J20" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K20" t="n">
-        <v>790.1259849731395</v>
+        <v>1216.127674193434</v>
       </c>
       <c r="L20" t="n">
-        <v>1020.623267284697</v>
+        <v>1446.624956504992</v>
       </c>
       <c r="M20" t="n">
-        <v>1669.073267284698</v>
+        <v>1446.624956504992</v>
       </c>
       <c r="N20" t="n">
-        <v>2233.691587554866</v>
+        <v>1446.624956504992</v>
       </c>
       <c r="O20" t="n">
-        <v>2410.244759641338</v>
+        <v>2095.074956504992</v>
       </c>
       <c r="P20" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="Q20" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="R20" t="n">
         <v>2620</v>
       </c>
       <c r="S20" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T20" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U20" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V20" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W20" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X20" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y20" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1050.16013417974</v>
+        <v>405.7156897352961</v>
       </c>
       <c r="C21" t="n">
-        <v>1007.634970093357</v>
+        <v>363.1905256489129</v>
       </c>
       <c r="D21" t="n">
-        <v>656.1827611057788</v>
+        <v>333.9605388835567</v>
       </c>
       <c r="E21" t="n">
-        <v>310.0493295684933</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F21" t="n">
         <v>64.01042542894548</v>
       </c>
       <c r="G21" t="n">
-        <v>58.00018335964016</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H21" t="n">
         <v>52.4</v>
@@ -5855,19 +5855,19 @@
         <v>1914.658037974811</v>
       </c>
       <c r="U21" t="n">
-        <v>1832.679830098122</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V21" t="n">
-        <v>1736.204408692546</v>
+        <v>1091.759964248101</v>
       </c>
       <c r="W21" t="n">
-        <v>1621.686082521002</v>
+        <v>655.019415854335</v>
       </c>
       <c r="X21" t="n">
-        <v>1519.804527525661</v>
+        <v>553.137860858994</v>
       </c>
       <c r="Y21" t="n">
-        <v>1438.601100489161</v>
+        <v>471.9344338224947</v>
       </c>
     </row>
     <row r="22">
@@ -5877,31 +5877,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C22" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D22" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E22" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F22" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G22" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H22" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I22" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J22" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K22" t="n">
         <v>1597.372803794637</v>
@@ -5910,22 +5910,22 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M22" t="n">
-        <v>1492.275360291076</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N22" t="n">
         <v>1339.839881046618</v>
       </c>
       <c r="O22" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P22" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q22" t="n">
-        <v>466.2233328154396</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R22" t="n">
-        <v>84.56167017509824</v>
+        <v>81.68251716755645</v>
       </c>
       <c r="S22" t="n">
         <v>52.4</v>
@@ -5934,19 +5934,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U22" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V22" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W22" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X22" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y22" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="23">
@@ -5956,19 +5956,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>607.5035534240029</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C23" t="n">
-        <v>475.7110501482515</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D23" t="n">
-        <v>383.4492766736557</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E23" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F23" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G23" t="n">
         <v>127.0464193797368</v>
@@ -5992,13 +5992,13 @@
         <v>1438.575984973139</v>
       </c>
       <c r="N23" t="n">
-        <v>1761.794759641278</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O23" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P23" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q23" t="n">
         <v>2620</v>
@@ -6007,25 +6007,25 @@
         <v>2620</v>
       </c>
       <c r="S23" t="n">
-        <v>2476.335336314592</v>
+        <v>2477.038452472668</v>
       </c>
       <c r="T23" t="n">
-        <v>2212.479660135798</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.04201730968</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.051083807838</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W23" t="n">
-        <v>1242.451613120012</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X23" t="n">
-        <v>966.4093570991351</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y23" t="n">
-        <v>772.1493240861994</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="24">
@@ -6035,25 +6035,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>654.8939430267878</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C24" t="n">
-        <v>612.3687789404047</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D24" t="n">
-        <v>583.1387921750485</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E24" t="n">
-        <v>559.2275828599852</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F24" t="n">
-        <v>538.3828936298065</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G24" t="n">
-        <v>532.3726515605013</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H24" t="n">
-        <v>204.5502459786388</v>
+        <v>52.4</v>
       </c>
       <c r="I24" t="n">
         <v>52.4</v>
@@ -6080,31 +6080,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2240.946636437805</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2059.873923335154</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S24" t="n">
-        <v>1925.630174562057</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T24" t="n">
-        <v>1841.614069044081</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U24" t="n">
-        <v>1437.413638945169</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V24" t="n">
-        <v>1018.715995317371</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W24" t="n">
-        <v>904.1976691458267</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X24" t="n">
-        <v>802.3161141504858</v>
+        <v>1294.610312616292</v>
       </c>
       <c r="Y24" t="n">
-        <v>721.1126871139865</v>
+        <v>891.1846633575699</v>
       </c>
     </row>
     <row r="25">
@@ -6114,31 +6114,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C25" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D25" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E25" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F25" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G25" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H25" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I25" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J25" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K25" t="n">
         <v>1597.372803794637</v>
@@ -6147,7 +6147,7 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M25" t="n">
-        <v>1492.275360291075</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N25" t="n">
         <v>1339.839881046618</v>
@@ -6162,7 +6162,7 @@
         <v>463.3441798078979</v>
       </c>
       <c r="R25" t="n">
-        <v>81.68251716755645</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S25" t="n">
         <v>52.4</v>
@@ -6171,19 +6171,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U25" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V25" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W25" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X25" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y25" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>607.5035534240307</v>
+        <v>607.5035534240279</v>
       </c>
       <c r="C26" t="n">
-        <v>475.7110501482792</v>
+        <v>475.7110501482765</v>
       </c>
       <c r="D26" t="n">
-        <v>383.4492766736835</v>
+        <v>383.4492766736807</v>
       </c>
       <c r="E26" t="n">
-        <v>297.2237316162404</v>
+        <v>297.2237316162377</v>
       </c>
       <c r="F26" t="n">
-        <v>210.4665309010769</v>
+        <v>210.4665309010742</v>
       </c>
       <c r="G26" t="n">
-        <v>127.0464193797378</v>
+        <v>127.0464193797374</v>
       </c>
       <c r="H26" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="I26" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="J26" t="n">
-        <v>567.6776741934355</v>
+        <v>141.67598497314</v>
       </c>
       <c r="K26" t="n">
-        <v>753.4744118316264</v>
+        <v>790.1259849731462</v>
       </c>
       <c r="L26" t="n">
-        <v>983.9716941431842</v>
+        <v>1438.575984973152</v>
       </c>
       <c r="M26" t="n">
-        <v>1632.42169414319</v>
+        <v>2087.025984973158</v>
       </c>
       <c r="N26" t="n">
-        <v>1637.361628029806</v>
+        <v>2233.691587554832</v>
       </c>
       <c r="O26" t="n">
-        <v>1813.914800116278</v>
+        <v>2410.244759641304</v>
       </c>
       <c r="P26" t="n">
-        <v>2023.670040474999</v>
+        <v>2620.000000000025</v>
       </c>
       <c r="Q26" t="n">
-        <v>2620.000000000028</v>
+        <v>2620.000000000025</v>
       </c>
       <c r="R26" t="n">
-        <v>2620.000000000028</v>
+        <v>2620.000000000025</v>
       </c>
       <c r="S26" t="n">
-        <v>2476.33533631462</v>
+        <v>2476.335336314617</v>
       </c>
       <c r="T26" t="n">
-        <v>2212.479660135826</v>
+        <v>2212.479660135823</v>
       </c>
       <c r="U26" t="n">
-        <v>1879.042017309708</v>
+        <v>1879.042017309705</v>
       </c>
       <c r="V26" t="n">
-        <v>1565.051083807865</v>
+        <v>1565.051083807863</v>
       </c>
       <c r="W26" t="n">
-        <v>1242.451613120039</v>
+        <v>1242.451613120037</v>
       </c>
       <c r="X26" t="n">
-        <v>966.4093570991629</v>
+        <v>966.4093570991602</v>
       </c>
       <c r="Y26" t="n">
-        <v>772.1493240862271</v>
+        <v>772.1493240862244</v>
       </c>
     </row>
     <row r="27">
@@ -6272,34 +6272,34 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1050.160134179741</v>
+        <v>1147.188141492594</v>
       </c>
       <c r="C27" t="n">
-        <v>685.4127478711359</v>
+        <v>782.4407551839886</v>
       </c>
       <c r="D27" t="n">
-        <v>430.9885461964106</v>
+        <v>753.2107684186324</v>
       </c>
       <c r="E27" t="n">
-        <v>407.0773368813473</v>
+        <v>407.0773368813469</v>
       </c>
       <c r="F27" t="n">
-        <v>64.01042542894642</v>
+        <v>64.01042542894598</v>
       </c>
       <c r="G27" t="n">
-        <v>58.00018335964111</v>
+        <v>58.00018335964068</v>
       </c>
       <c r="H27" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="I27" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="J27" t="n">
-        <v>250.1913459300169</v>
+        <v>250.1913459300164</v>
       </c>
       <c r="K27" t="n">
-        <v>565.5796394772306</v>
+        <v>565.5796394772301</v>
       </c>
       <c r="L27" t="n">
         <v>1006.615493996959</v>
@@ -6314,16 +6314,16 @@
         <v>2052.228604861294</v>
       </c>
       <c r="P27" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R27" t="n">
-        <v>2132.917892265886</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S27" t="n">
-        <v>1998.674143492789</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T27" t="n">
         <v>1914.658037974812</v>
@@ -6332,13 +6332,13 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V27" t="n">
-        <v>1736.204408692547</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W27" t="n">
-        <v>1621.686082521003</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X27" t="n">
-        <v>1519.804527525662</v>
+        <v>1519.804527525661</v>
       </c>
       <c r="Y27" t="n">
         <v>1438.601100489162</v>
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>673.4417775581354</v>
+        <v>673.441777558135</v>
       </c>
       <c r="C28" t="n">
-        <v>719.2537833765712</v>
+        <v>719.2537833765707</v>
       </c>
       <c r="D28" t="n">
-        <v>752.3829275015712</v>
+        <v>752.3829275015707</v>
       </c>
       <c r="E28" t="n">
-        <v>790.0218317129842</v>
+        <v>790.0218317129837</v>
       </c>
       <c r="F28" t="n">
-        <v>834.1928043049197</v>
+        <v>834.1928043049193</v>
       </c>
       <c r="G28" t="n">
-        <v>908.0645554377066</v>
+        <v>908.0645554377062</v>
       </c>
       <c r="H28" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I28" t="n">
         <v>1163.862419205318</v>
       </c>
       <c r="J28" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K28" t="n">
         <v>1597.372803794638</v>
       </c>
       <c r="L28" t="n">
-        <v>1591.155096928857</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M28" t="n">
-        <v>1492.275360291077</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N28" t="n">
         <v>1339.839881046619</v>
       </c>
       <c r="O28" t="n">
-        <v>1109.635154952566</v>
+        <v>1109.635154952565</v>
       </c>
       <c r="P28" t="n">
-        <v>818.3161660963821</v>
+        <v>818.3161660963816</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.3441798078993</v>
+        <v>463.3441798078988</v>
       </c>
       <c r="R28" t="n">
-        <v>81.68251716755782</v>
+        <v>84.56167017509873</v>
       </c>
       <c r="S28" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="T28" t="n">
-        <v>163.0851070276582</v>
+        <v>163.0851070276578</v>
       </c>
       <c r="U28" t="n">
-        <v>329.4820370429941</v>
+        <v>329.4820370429936</v>
       </c>
       <c r="V28" t="n">
-        <v>448.11342992894</v>
+        <v>448.1134299289396</v>
       </c>
       <c r="W28" t="n">
-        <v>539.8143481886175</v>
+        <v>539.814348188617</v>
       </c>
       <c r="X28" t="n">
-        <v>610.655139212811</v>
+        <v>610.6551392128106</v>
       </c>
       <c r="Y28" t="n">
-        <v>641.8744398918433</v>
+        <v>641.8744398918428</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>608.2066695820796</v>
+        <v>607.5035534240279</v>
       </c>
       <c r="C29" t="n">
-        <v>476.4141663063281</v>
+        <v>475.7110501482765</v>
       </c>
       <c r="D29" t="n">
-        <v>384.1523928317324</v>
+        <v>383.4492766736807</v>
       </c>
       <c r="E29" t="n">
-        <v>297.9268477742893</v>
+        <v>297.2237316162377</v>
       </c>
       <c r="F29" t="n">
-        <v>211.1696470591258</v>
+        <v>210.4665309010742</v>
       </c>
       <c r="G29" t="n">
-        <v>127.0464193797378</v>
+        <v>127.0464193797374</v>
       </c>
       <c r="H29" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="I29" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="J29" t="n">
-        <v>141.6759849731404</v>
+        <v>141.67598497314</v>
       </c>
       <c r="K29" t="n">
-        <v>327.4727226113314</v>
+        <v>790.1259849731462</v>
       </c>
       <c r="L29" t="n">
-        <v>557.9700049228892</v>
+        <v>1020.623267284704</v>
       </c>
       <c r="M29" t="n">
-        <v>1206.4200049229</v>
+        <v>1020.623267284704</v>
       </c>
       <c r="N29" t="n">
-        <v>1854.870004922911</v>
+        <v>1637.361628029803</v>
       </c>
       <c r="O29" t="n">
-        <v>2031.423177009384</v>
+        <v>1813.914800116276</v>
       </c>
       <c r="P29" t="n">
-        <v>2620.000000000047</v>
+        <v>2023.670040474996</v>
       </c>
       <c r="Q29" t="n">
-        <v>2620.000000000047</v>
+        <v>2620.000000000025</v>
       </c>
       <c r="R29" t="n">
-        <v>2620.000000000047</v>
+        <v>2620.000000000025</v>
       </c>
       <c r="S29" t="n">
-        <v>2477.038452472669</v>
+        <v>2476.335336314617</v>
       </c>
       <c r="T29" t="n">
-        <v>2213.182776293875</v>
+        <v>2212.479660135823</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.745133467757</v>
+        <v>1879.042017309705</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.754199965914</v>
+        <v>1565.051083807863</v>
       </c>
       <c r="W29" t="n">
-        <v>1243.154729278088</v>
+        <v>1242.451613120037</v>
       </c>
       <c r="X29" t="n">
-        <v>967.1124732572118</v>
+        <v>966.4093570991602</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.8524402442761</v>
+        <v>772.1493240862244</v>
       </c>
     </row>
     <row r="30">
@@ -6509,34 +6509,34 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1050.160134179742</v>
+        <v>1050.160134179741</v>
       </c>
       <c r="C30" t="n">
         <v>1007.634970093358</v>
       </c>
       <c r="D30" t="n">
-        <v>978.4049833280022</v>
+        <v>656.1827611057793</v>
       </c>
       <c r="E30" t="n">
-        <v>632.2715517907168</v>
+        <v>632.271551790716</v>
       </c>
       <c r="F30" t="n">
-        <v>289.2046403383159</v>
+        <v>611.4268625605373</v>
       </c>
       <c r="G30" t="n">
-        <v>283.1943982690105</v>
+        <v>572.088680638876</v>
       </c>
       <c r="H30" t="n">
-        <v>52.40000000000094</v>
+        <v>244.2662750570135</v>
       </c>
       <c r="I30" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="J30" t="n">
-        <v>250.1913459300169</v>
+        <v>250.1913459300164</v>
       </c>
       <c r="K30" t="n">
-        <v>565.5796394772306</v>
+        <v>565.5796394772301</v>
       </c>
       <c r="L30" t="n">
         <v>1006.615493996959</v>
@@ -6551,16 +6551,16 @@
         <v>2052.228604861294</v>
       </c>
       <c r="P30" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R30" t="n">
-        <v>2132.917892265886</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S30" t="n">
-        <v>1998.674143492789</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T30" t="n">
         <v>1914.658037974812</v>
@@ -6569,7 +6569,7 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V30" t="n">
-        <v>1736.204408692547</v>
+        <v>1413.982186470324</v>
       </c>
       <c r="W30" t="n">
         <v>1299.46386029878</v>
@@ -6578,7 +6578,7 @@
         <v>1197.582305303439</v>
       </c>
       <c r="Y30" t="n">
-        <v>1116.37887826694</v>
+        <v>1116.378878266939</v>
       </c>
     </row>
     <row r="31">
@@ -6588,37 +6588,37 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>673.4417775581354</v>
+        <v>673.441777558135</v>
       </c>
       <c r="C31" t="n">
-        <v>719.2537833765712</v>
+        <v>719.2537833765707</v>
       </c>
       <c r="D31" t="n">
-        <v>752.3829275015712</v>
+        <v>752.3829275015707</v>
       </c>
       <c r="E31" t="n">
-        <v>790.0218317129842</v>
+        <v>790.0218317129837</v>
       </c>
       <c r="F31" t="n">
-        <v>834.1928043049197</v>
+        <v>834.1928043049193</v>
       </c>
       <c r="G31" t="n">
-        <v>908.0645554377066</v>
+        <v>908.0645554377062</v>
       </c>
       <c r="H31" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I31" t="n">
         <v>1163.862419205318</v>
       </c>
       <c r="J31" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K31" t="n">
         <v>1597.372803794638</v>
       </c>
       <c r="L31" t="n">
-        <v>1591.155096928857</v>
+        <v>1594.034249936398</v>
       </c>
       <c r="M31" t="n">
         <v>1495.154513298618</v>
@@ -6630,34 +6630,34 @@
         <v>1112.514307960107</v>
       </c>
       <c r="P31" t="n">
-        <v>821.1953191039233</v>
+        <v>821.1953191039229</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.2233328154406</v>
+        <v>466.2233328154401</v>
       </c>
       <c r="R31" t="n">
-        <v>84.56167017509917</v>
+        <v>84.56167017509873</v>
       </c>
       <c r="S31" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="T31" t="n">
-        <v>163.0851070276582</v>
+        <v>163.0851070276578</v>
       </c>
       <c r="U31" t="n">
-        <v>329.4820370429941</v>
+        <v>329.4820370429936</v>
       </c>
       <c r="V31" t="n">
-        <v>448.11342992894</v>
+        <v>448.1134299289396</v>
       </c>
       <c r="W31" t="n">
-        <v>539.8143481886175</v>
+        <v>539.814348188617</v>
       </c>
       <c r="X31" t="n">
-        <v>610.655139212811</v>
+        <v>610.6551392128106</v>
       </c>
       <c r="Y31" t="n">
-        <v>641.8744398918433</v>
+        <v>641.8744398918428</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>608.2066695820795</v>
+        <v>607.5035534241052</v>
       </c>
       <c r="C32" t="n">
-        <v>476.4141663063281</v>
+        <v>475.7110501483538</v>
       </c>
       <c r="D32" t="n">
-        <v>384.1523928317323</v>
+        <v>383.449276673758</v>
       </c>
       <c r="E32" t="n">
-        <v>297.9268477742892</v>
+        <v>297.223731616315</v>
       </c>
       <c r="F32" t="n">
-        <v>211.1696470591257</v>
+        <v>210.4665309011515</v>
       </c>
       <c r="G32" t="n">
-        <v>127.0464193797378</v>
+        <v>126.3433032217635</v>
       </c>
       <c r="H32" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="I32" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="J32" t="n">
-        <v>141.6759849731404</v>
+        <v>141.67598497314</v>
       </c>
       <c r="K32" t="n">
-        <v>706.2943052432672</v>
+        <v>327.4727226113309</v>
       </c>
       <c r="L32" t="n">
-        <v>936.791587554825</v>
+        <v>936.7915875547959</v>
       </c>
       <c r="M32" t="n">
-        <v>1585.241587554839</v>
+        <v>1585.241587554814</v>
       </c>
       <c r="N32" t="n">
-        <v>2233.691587554854</v>
+        <v>2233.691587554832</v>
       </c>
       <c r="O32" t="n">
-        <v>2410.244759641326</v>
+        <v>2410.244759641304</v>
       </c>
       <c r="P32" t="n">
-        <v>2620.000000000047</v>
+        <v>2620.000000000025</v>
       </c>
       <c r="Q32" t="n">
-        <v>2620.000000000047</v>
+        <v>2620.000000000025</v>
       </c>
       <c r="R32" t="n">
-        <v>2620.000000000047</v>
+        <v>2620.000000000102</v>
       </c>
       <c r="S32" t="n">
-        <v>2476.335336314639</v>
+        <v>2476.335336314694</v>
       </c>
       <c r="T32" t="n">
-        <v>2212.479660135845</v>
+        <v>2212.4796601359</v>
       </c>
       <c r="U32" t="n">
-        <v>1879.745133467757</v>
+        <v>1879.042017309782</v>
       </c>
       <c r="V32" t="n">
-        <v>1565.754199965914</v>
+        <v>1565.05108380794</v>
       </c>
       <c r="W32" t="n">
-        <v>1243.154729278088</v>
+        <v>1242.451613120114</v>
       </c>
       <c r="X32" t="n">
-        <v>967.1124732572117</v>
+        <v>966.4093570992375</v>
       </c>
       <c r="Y32" t="n">
-        <v>772.852440244276</v>
+        <v>772.1493240863017</v>
       </c>
     </row>
     <row r="33">
@@ -6746,34 +6746,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>654.8939430267887</v>
+        <v>1016.832194327385</v>
       </c>
       <c r="C33" t="n">
-        <v>612.3687789404056</v>
+        <v>652.0848080187793</v>
       </c>
       <c r="D33" t="n">
-        <v>260.9165699528272</v>
+        <v>622.8548212534231</v>
       </c>
       <c r="E33" t="n">
-        <v>237.0053606377639</v>
+        <v>276.7213897161377</v>
       </c>
       <c r="F33" t="n">
-        <v>216.1606714075853</v>
+        <v>255.876700485959</v>
       </c>
       <c r="G33" t="n">
-        <v>58.0001833596411</v>
+        <v>249.8664584166537</v>
       </c>
       <c r="H33" t="n">
-        <v>52.40000000000094</v>
+        <v>244.2662750570135</v>
       </c>
       <c r="I33" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="J33" t="n">
-        <v>250.1913459300169</v>
+        <v>250.1913459300164</v>
       </c>
       <c r="K33" t="n">
-        <v>565.5796394772306</v>
+        <v>565.5796394772301</v>
       </c>
       <c r="L33" t="n">
         <v>1006.615493996959</v>
@@ -6788,34 +6788,34 @@
         <v>2052.228604861294</v>
       </c>
       <c r="P33" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2240.946636437806</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R33" t="n">
-        <v>2059.873923335155</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S33" t="n">
-        <v>1925.630174562058</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T33" t="n">
-        <v>1841.614069044082</v>
+        <v>1914.658037974812</v>
       </c>
       <c r="U33" t="n">
-        <v>1437.41363894517</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V33" t="n">
-        <v>1018.715995317372</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W33" t="n">
-        <v>904.1976691458276</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X33" t="n">
-        <v>802.3161141504867</v>
+        <v>1519.804527525661</v>
       </c>
       <c r="Y33" t="n">
-        <v>721.1126871139874</v>
+        <v>1116.378878266939</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>673.4417775581354</v>
+        <v>673.441777558135</v>
       </c>
       <c r="C34" t="n">
-        <v>719.2537833765832</v>
+        <v>719.2537833765707</v>
       </c>
       <c r="D34" t="n">
-        <v>752.3829275015833</v>
+        <v>752.3829275015707</v>
       </c>
       <c r="E34" t="n">
-        <v>790.0218317129962</v>
+        <v>790.0218317129837</v>
       </c>
       <c r="F34" t="n">
-        <v>834.1928043049318</v>
+        <v>834.1928043049193</v>
       </c>
       <c r="G34" t="n">
-        <v>908.0645554377187</v>
+        <v>908.0645554377062</v>
       </c>
       <c r="H34" t="n">
-        <v>1003.216333056133</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I34" t="n">
-        <v>1163.86241920533</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J34" t="n">
-        <v>1491.077756743028</v>
+        <v>1491.07775674302</v>
       </c>
       <c r="K34" t="n">
-        <v>1597.37280379465</v>
+        <v>1597.372803794643</v>
       </c>
       <c r="L34" t="n">
-        <v>1591.155096928869</v>
+        <v>1591.155096928862</v>
       </c>
       <c r="M34" t="n">
-        <v>1492.275360291088</v>
+        <v>1492.275360291082</v>
       </c>
       <c r="N34" t="n">
-        <v>1339.839881046631</v>
+        <v>1339.839881046624</v>
       </c>
       <c r="O34" t="n">
-        <v>1109.635154952577</v>
+        <v>1109.63515495257</v>
       </c>
       <c r="P34" t="n">
-        <v>818.3161660963934</v>
+        <v>818.3161660963866</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.3441798079106</v>
+        <v>463.3441798079038</v>
       </c>
       <c r="R34" t="n">
-        <v>81.68251716756924</v>
+        <v>81.68251716756242</v>
       </c>
       <c r="S34" t="n">
-        <v>52.40000000000094</v>
+        <v>52.4000000000005</v>
       </c>
       <c r="T34" t="n">
-        <v>163.0851070276583</v>
+        <v>163.0851070276578</v>
       </c>
       <c r="U34" t="n">
-        <v>329.4820370429941</v>
+        <v>329.4820370429936</v>
       </c>
       <c r="V34" t="n">
-        <v>448.11342992894</v>
+        <v>448.1134299289396</v>
       </c>
       <c r="W34" t="n">
-        <v>539.8143481886175</v>
+        <v>539.814348188617</v>
       </c>
       <c r="X34" t="n">
-        <v>610.655139212811</v>
+        <v>610.6551392128106</v>
       </c>
       <c r="Y34" t="n">
-        <v>641.8744398918433</v>
+        <v>641.8744398918428</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>113.8065837270799</v>
+        <v>113.806583727058</v>
       </c>
       <c r="C35" t="n">
-        <v>60.80195923920722</v>
+        <v>60.80195923918539</v>
       </c>
       <c r="D35" t="n">
-        <v>47.32806455249026</v>
+        <v>47.32806455246843</v>
       </c>
       <c r="E35" t="n">
-        <v>39.89039828292597</v>
+        <v>43.22467081879439</v>
       </c>
       <c r="F35" t="n">
-        <v>35.25534889151013</v>
+        <v>35.25534889150969</v>
       </c>
       <c r="G35" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="H35" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="I35" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="J35" t="n">
-        <v>119.1959849731404</v>
+        <v>119.19598497314</v>
       </c>
       <c r="K35" t="n">
-        <v>304.9927226113313</v>
+        <v>304.9927226113309</v>
       </c>
       <c r="L35" t="n">
-        <v>535.4900049228892</v>
+        <v>535.4900049228887</v>
       </c>
       <c r="M35" t="n">
-        <v>739.4315875548195</v>
+        <v>739.4315875547888</v>
       </c>
       <c r="N35" t="n">
-        <v>739.4315875548195</v>
+        <v>1109.691587554832</v>
       </c>
       <c r="O35" t="n">
-        <v>915.9847596412922</v>
+        <v>1286.244759641305</v>
       </c>
       <c r="P35" t="n">
-        <v>1125.740000000013</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="Q35" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="R35" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="S35" t="n">
-        <v>1431.123215102517</v>
+        <v>1431.123215102496</v>
       </c>
       <c r="T35" t="n">
-        <v>1246.055417711602</v>
+        <v>1246.05541771158</v>
       </c>
       <c r="U35" t="n">
-        <v>991.4056536733628</v>
+        <v>991.405653673341</v>
       </c>
       <c r="V35" t="n">
-        <v>756.2025989593993</v>
+        <v>756.2025989593775</v>
       </c>
       <c r="W35" t="n">
-        <v>512.3910070594522</v>
+        <v>512.3910070594304</v>
       </c>
       <c r="X35" t="n">
-        <v>315.1366298264545</v>
+        <v>315.1366298264327</v>
       </c>
       <c r="Y35" t="n">
-        <v>199.6644756013976</v>
+        <v>199.6644756013757</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>873.13574764589</v>
+        <v>424.7295491859275</v>
       </c>
       <c r="C36" t="n">
-        <v>508.3883613372846</v>
+        <v>424.7295491859275</v>
       </c>
       <c r="D36" t="n">
-        <v>508.3883613372846</v>
+        <v>424.7295491859275</v>
       </c>
       <c r="E36" t="n">
-        <v>221.7862750570139</v>
+        <v>424.7295491859275</v>
       </c>
       <c r="F36" t="n">
-        <v>221.7862750570139</v>
+        <v>424.7295491859275</v>
       </c>
       <c r="G36" t="n">
-        <v>221.7862750570139</v>
+        <v>424.7295491859275</v>
       </c>
       <c r="H36" t="n">
-        <v>221.7862750570139</v>
+        <v>221.7862750570135</v>
       </c>
       <c r="I36" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="J36" t="n">
-        <v>227.7113459300169</v>
+        <v>227.7113459300164</v>
       </c>
       <c r="K36" t="n">
-        <v>543.0996394772305</v>
+        <v>250.1782010228467</v>
       </c>
       <c r="L36" t="n">
-        <v>599.9270509017589</v>
+        <v>527.4420010172464</v>
       </c>
       <c r="M36" t="n">
-        <v>884.0224426446182</v>
+        <v>527.4420010172464</v>
       </c>
       <c r="N36" t="n">
-        <v>1188.111259659716</v>
+        <v>863.9779994927392</v>
       </c>
       <c r="O36" t="n">
-        <v>1234.237999492804</v>
+        <v>1234.237999492782</v>
       </c>
       <c r="P36" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="Q36" t="n">
-        <v>1496.000000000047</v>
+        <v>1422.956031069295</v>
       </c>
       <c r="R36" t="n">
-        <v>1393.715165685275</v>
+        <v>1320.671196754522</v>
       </c>
       <c r="S36" t="n">
-        <v>1338.259295700056</v>
+        <v>1265.215326769304</v>
       </c>
       <c r="T36" t="n">
-        <v>1333.031068969959</v>
+        <v>1259.987100039207</v>
       </c>
       <c r="U36" t="n">
-        <v>1329.840739881148</v>
+        <v>1256.796770950396</v>
       </c>
       <c r="V36" t="n">
-        <v>1312.153197263451</v>
+        <v>1239.109228332699</v>
       </c>
       <c r="W36" t="n">
-        <v>1276.422749879785</v>
+        <v>1203.378780949033</v>
       </c>
       <c r="X36" t="n">
-        <v>1253.329073672323</v>
+        <v>1180.285104741571</v>
       </c>
       <c r="Y36" t="n">
-        <v>1250.913525423703</v>
+        <v>802.5073269637494</v>
       </c>
     </row>
     <row r="37">
@@ -7062,16 +7062,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>944.91082537133</v>
+        <v>585.6289427495453</v>
       </c>
       <c r="C37" t="n">
-        <v>944.91082537133</v>
+        <v>708.6609485679811</v>
       </c>
       <c r="D37" t="n">
-        <v>1055.25996949633</v>
+        <v>819.0100926929812</v>
       </c>
       <c r="E37" t="n">
-        <v>1055.25996949633</v>
+        <v>933.8689969043942</v>
       </c>
       <c r="F37" t="n">
         <v>1055.25996949633</v>
@@ -7098,40 +7098,40 @@
         <v>1046.573449184126</v>
       </c>
       <c r="N37" t="n">
-        <v>972.9258487275475</v>
+        <v>972.9258487275471</v>
       </c>
       <c r="O37" t="n">
-        <v>821.5090014213724</v>
+        <v>821.509001421372</v>
       </c>
       <c r="P37" t="n">
-        <v>608.9778913530675</v>
+        <v>608.9778913530671</v>
       </c>
       <c r="Q37" t="n">
-        <v>332.7937838524635</v>
+        <v>332.7937838524631</v>
       </c>
       <c r="R37" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="S37" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="T37" t="n">
-        <v>214.8510848561887</v>
+        <v>217.8251070276578</v>
       </c>
       <c r="U37" t="n">
-        <v>214.8510848561887</v>
+        <v>280.9902121973072</v>
       </c>
       <c r="V37" t="n">
-        <v>410.7024777421347</v>
+        <v>476.8416050832532</v>
       </c>
       <c r="W37" t="n">
-        <v>579.6233960018121</v>
+        <v>476.8416050832532</v>
       </c>
       <c r="X37" t="n">
-        <v>727.6841870260056</v>
+        <v>476.8416050832532</v>
       </c>
       <c r="Y37" t="n">
-        <v>836.1234877050379</v>
+        <v>476.8416050832532</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>113.8065837270799</v>
+        <v>113.806583727058</v>
       </c>
       <c r="C38" t="n">
-        <v>60.80195923920722</v>
+        <v>60.80195923918539</v>
       </c>
       <c r="D38" t="n">
-        <v>47.32806455249026</v>
+        <v>47.32806455246843</v>
       </c>
       <c r="E38" t="n">
-        <v>39.89039828292597</v>
+        <v>39.89039828290414</v>
       </c>
       <c r="F38" t="n">
-        <v>35.25534889151013</v>
+        <v>35.25534889150967</v>
       </c>
       <c r="G38" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="H38" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="I38" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="J38" t="n">
-        <v>119.1959849731404</v>
+        <v>119.19598497314</v>
       </c>
       <c r="K38" t="n">
-        <v>304.9927226113313</v>
+        <v>489.4559849731461</v>
       </c>
       <c r="L38" t="n">
-        <v>535.4900049228892</v>
+        <v>719.9532672847039</v>
       </c>
       <c r="M38" t="n">
-        <v>739.4315875547998</v>
+        <v>739.4315875547618</v>
       </c>
       <c r="N38" t="n">
-        <v>1109.691587554854</v>
+        <v>1109.691587554832</v>
       </c>
       <c r="O38" t="n">
-        <v>1286.244759641326</v>
+        <v>1286.244759641305</v>
       </c>
       <c r="P38" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="Q38" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="R38" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="S38" t="n">
-        <v>1431.123215102517</v>
+        <v>1431.123215102496</v>
       </c>
       <c r="T38" t="n">
-        <v>1246.055417711602</v>
+        <v>1246.05541771158</v>
       </c>
       <c r="U38" t="n">
-        <v>991.4056536733628</v>
+        <v>991.4056536733409</v>
       </c>
       <c r="V38" t="n">
-        <v>756.2025989593993</v>
+        <v>756.2025989593774</v>
       </c>
       <c r="W38" t="n">
-        <v>512.3910070594522</v>
+        <v>512.3910070594304</v>
       </c>
       <c r="X38" t="n">
-        <v>315.1366298264545</v>
+        <v>315.1366298264327</v>
       </c>
       <c r="Y38" t="n">
-        <v>199.6644756013976</v>
+        <v>199.6644756013757</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1177.869556492973</v>
+        <v>1089.186506748585</v>
       </c>
       <c r="C39" t="n">
-        <v>1070.572551977266</v>
+        <v>724.4391204399799</v>
       </c>
       <c r="D39" t="n">
-        <v>719.1203429896873</v>
+        <v>372.9869114524014</v>
       </c>
       <c r="E39" t="n">
-        <v>372.9869114524018</v>
+        <v>372.9869114524014</v>
       </c>
       <c r="F39" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="G39" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="H39" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="I39" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="J39" t="n">
-        <v>67.57895890365782</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="K39" t="n">
-        <v>90.04581399648805</v>
+        <v>52.38685509283073</v>
       </c>
       <c r="L39" t="n">
-        <v>460.3058139965421</v>
+        <v>422.646855092901</v>
       </c>
       <c r="M39" t="n">
-        <v>744.4012057394013</v>
+        <v>706.7422468357603</v>
       </c>
       <c r="N39" t="n">
-        <v>1080.937204214894</v>
+        <v>1043.278245311253</v>
       </c>
       <c r="O39" t="n">
-        <v>1451.197204214948</v>
+        <v>1234.237999492782</v>
       </c>
       <c r="P39" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="Q39" t="n">
-        <v>1422.956031069317</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="R39" t="n">
-        <v>1320.671196754544</v>
+        <v>1393.715165685253</v>
       </c>
       <c r="S39" t="n">
-        <v>1265.215326769326</v>
+        <v>1338.259295700034</v>
       </c>
       <c r="T39" t="n">
-        <v>1259.987100039228</v>
+        <v>1333.031068969937</v>
       </c>
       <c r="U39" t="n">
-        <v>1256.796770950418</v>
+        <v>1329.840739881126</v>
       </c>
       <c r="V39" t="n">
-        <v>1239.10922833272</v>
+        <v>1312.153197263429</v>
       </c>
       <c r="W39" t="n">
-        <v>1203.378780949055</v>
+        <v>1276.422749879764</v>
       </c>
       <c r="X39" t="n">
-        <v>1180.285104741593</v>
+        <v>1091.602054997206</v>
       </c>
       <c r="Y39" t="n">
-        <v>1177.869556492973</v>
+        <v>1089.186506748585</v>
       </c>
     </row>
     <row r="40">
@@ -7299,25 +7299,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>326.6124446939504</v>
+        <v>544.8863357417586</v>
       </c>
       <c r="C40" t="n">
-        <v>449.6444505123861</v>
+        <v>667.9183415601943</v>
       </c>
       <c r="D40" t="n">
-        <v>449.6444505123861</v>
+        <v>667.9183415601943</v>
       </c>
       <c r="E40" t="n">
-        <v>564.5033547237991</v>
+        <v>782.7772457716073</v>
       </c>
       <c r="F40" t="n">
-        <v>685.8943273157346</v>
+        <v>904.1682183635428</v>
       </c>
       <c r="G40" t="n">
-        <v>836.9860784485215</v>
+        <v>1055.25996949633</v>
       </c>
       <c r="H40" t="n">
-        <v>836.9860784485215</v>
+        <v>1055.25996949633</v>
       </c>
       <c r="I40" t="n">
         <v>1055.25996949633</v>
@@ -7335,40 +7335,40 @@
         <v>1046.573449184126</v>
       </c>
       <c r="N40" t="n">
-        <v>972.9258487275475</v>
+        <v>972.9258487275471</v>
       </c>
       <c r="O40" t="n">
-        <v>821.5090014213724</v>
+        <v>821.509001421372</v>
       </c>
       <c r="P40" t="n">
-        <v>608.9778913530675</v>
+        <v>608.9778913530671</v>
       </c>
       <c r="Q40" t="n">
-        <v>332.7937838524635</v>
+        <v>332.7937838524631</v>
       </c>
       <c r="R40" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="S40" t="n">
-        <v>29.92000000000094</v>
+        <v>71.32668692984302</v>
       </c>
       <c r="T40" t="n">
-        <v>217.8251070276582</v>
+        <v>71.32668692984302</v>
       </c>
       <c r="U40" t="n">
-        <v>217.8251070276582</v>
+        <v>71.32668692984302</v>
       </c>
       <c r="V40" t="n">
-        <v>217.8251070276582</v>
+        <v>267.178079815789</v>
       </c>
       <c r="W40" t="n">
-        <v>217.8251070276582</v>
+        <v>436.0989980754664</v>
       </c>
       <c r="X40" t="n">
-        <v>217.8251070276582</v>
+        <v>436.0989980754664</v>
       </c>
       <c r="Y40" t="n">
-        <v>217.8251070276582</v>
+        <v>436.0989980754664</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.92000000000094</v>
+        <v>44.53386861214688</v>
       </c>
       <c r="C41" t="n">
-        <v>29.92000000000094</v>
+        <v>44.53386861214688</v>
       </c>
       <c r="D41" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="E41" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="F41" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="G41" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="H41" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="I41" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="J41" t="n">
-        <v>400.180000000073</v>
+        <v>400.1800000001086</v>
       </c>
       <c r="K41" t="n">
-        <v>585.976737638264</v>
+        <v>585.9767376382995</v>
       </c>
       <c r="L41" t="n">
-        <v>816.4740199498217</v>
+        <v>816.4740199498573</v>
       </c>
       <c r="M41" t="n">
-        <v>1109.691587554854</v>
+        <v>1109.691587554832</v>
       </c>
       <c r="N41" t="n">
-        <v>1109.691587554854</v>
+        <v>1109.691587554832</v>
       </c>
       <c r="O41" t="n">
-        <v>1286.244759641326</v>
+        <v>1286.244759641305</v>
       </c>
       <c r="P41" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="Q41" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="R41" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="S41" t="n">
-        <v>1496.000000000047</v>
+        <v>1326.07271005199</v>
       </c>
       <c r="T41" t="n">
-        <v>1381.040808087169</v>
+        <v>1035.95440761057</v>
       </c>
       <c r="U41" t="n">
-        <v>1021.340538998424</v>
+        <v>1035.95440761057</v>
       </c>
       <c r="V41" t="n">
-        <v>681.0869792339558</v>
+        <v>695.7008478461017</v>
       </c>
       <c r="W41" t="n">
-        <v>332.2248822835037</v>
+        <v>346.8387508956496</v>
       </c>
       <c r="X41" t="n">
-        <v>29.92000000000094</v>
+        <v>44.53386861214688</v>
       </c>
       <c r="Y41" t="n">
-        <v>29.92000000000094</v>
+        <v>44.53386861214688</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>318.0281146698374</v>
+        <v>315.6172324016848</v>
       </c>
       <c r="C42" t="n">
-        <v>249.240324320828</v>
+        <v>246.8294420526754</v>
       </c>
       <c r="D42" t="n">
-        <v>193.7477112928455</v>
+        <v>191.3368290246929</v>
       </c>
       <c r="E42" t="n">
-        <v>143.573875715156</v>
+        <v>141.1629934470034</v>
       </c>
       <c r="F42" t="n">
-        <v>94.05567795419896</v>
+        <v>94.0556779541985</v>
       </c>
       <c r="G42" t="n">
-        <v>61.78280962226738</v>
+        <v>61.78280962226692</v>
       </c>
       <c r="H42" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="I42" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="J42" t="n">
-        <v>227.7113459300169</v>
+        <v>227.7113459300164</v>
       </c>
       <c r="K42" t="n">
-        <v>543.0996394772305</v>
+        <v>543.0996394772301</v>
       </c>
       <c r="L42" t="n">
-        <v>599.9270509017589</v>
+        <v>599.9270509017584</v>
       </c>
       <c r="M42" t="n">
-        <v>851.5752611842231</v>
+        <v>851.5752611842013</v>
       </c>
       <c r="N42" t="n">
-        <v>1188.111259659716</v>
+        <v>1188.111259659694</v>
       </c>
       <c r="O42" t="n">
-        <v>1234.237999492804</v>
+        <v>1234.237999492782</v>
       </c>
       <c r="P42" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="Q42" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="R42" t="n">
-        <v>1288.664660634769</v>
+        <v>1288.664660634748</v>
       </c>
       <c r="S42" t="n">
-        <v>1128.158285599046</v>
+        <v>1128.158285599024</v>
       </c>
       <c r="T42" t="n">
-        <v>1017.879553818443</v>
+        <v>1017.879553818421</v>
       </c>
       <c r="U42" t="n">
-        <v>909.6387196791276</v>
+        <v>909.6387196791056</v>
       </c>
       <c r="V42" t="n">
-        <v>786.9006720109254</v>
+        <v>786.9006720109035</v>
       </c>
       <c r="W42" t="n">
-        <v>646.1197195767552</v>
+        <v>646.1197195767332</v>
       </c>
       <c r="X42" t="n">
-        <v>517.9755383187879</v>
+        <v>517.975538318766</v>
       </c>
       <c r="Y42" t="n">
-        <v>410.5094850196623</v>
+        <v>410.5094850196404</v>
       </c>
     </row>
     <row r="43">
@@ -7536,31 +7536,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>470.7817775581353</v>
+        <v>470.7817775581349</v>
       </c>
       <c r="C43" t="n">
-        <v>490.8537833765711</v>
+        <v>490.8537833765707</v>
       </c>
       <c r="D43" t="n">
-        <v>498.2429275015712</v>
+        <v>498.2429275015708</v>
       </c>
       <c r="E43" t="n">
-        <v>510.1418317129842</v>
+        <v>510.1418317129838</v>
       </c>
       <c r="F43" t="n">
-        <v>528.5728043049197</v>
+        <v>528.5728043049193</v>
       </c>
       <c r="G43" t="n">
-        <v>576.7045554377066</v>
+        <v>576.7045554377062</v>
       </c>
       <c r="H43" t="n">
-        <v>646.1163330561205</v>
+        <v>646.1163330561201</v>
       </c>
       <c r="I43" t="n">
-        <v>781.0224192053182</v>
+        <v>781.0224192053178</v>
       </c>
       <c r="J43" t="n">
-        <v>1082.497756743016</v>
+        <v>1082.497756743015</v>
       </c>
       <c r="K43" t="n">
         <v>1163.052803794638</v>
@@ -7572,40 +7572,40 @@
         <v>1163.052803794638</v>
       </c>
       <c r="N43" t="n">
-        <v>1100.367204350108</v>
+        <v>1163.052803794638</v>
       </c>
       <c r="O43" t="n">
-        <v>843.899851993428</v>
+        <v>1103.057170674587</v>
       </c>
       <c r="P43" t="n">
-        <v>843.899851993428</v>
+        <v>785.4755555557767</v>
       </c>
       <c r="Q43" t="n">
-        <v>466.1220742155767</v>
+        <v>407.6977777778886</v>
       </c>
       <c r="R43" t="n">
-        <v>88.34429643772542</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="S43" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="T43" t="n">
-        <v>114.8651070276583</v>
+        <v>114.8651070276578</v>
       </c>
       <c r="U43" t="n">
-        <v>255.522037042994</v>
+        <v>255.5220370429936</v>
       </c>
       <c r="V43" t="n">
-        <v>348.41342992894</v>
+        <v>348.4134299289396</v>
       </c>
       <c r="W43" t="n">
-        <v>414.3743481886174</v>
+        <v>414.374348188617</v>
       </c>
       <c r="X43" t="n">
-        <v>459.475139212811</v>
+        <v>459.4751392128105</v>
       </c>
       <c r="Y43" t="n">
-        <v>464.9544398918432</v>
+        <v>464.9544398918428</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>253.3256809198049</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="C44" t="n">
-        <v>253.3256809198049</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="D44" t="n">
-        <v>253.3256809198049</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="E44" t="n">
-        <v>253.3256809198049</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="F44" t="n">
-        <v>140.3058539420152</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="G44" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="H44" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="I44" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="J44" t="n">
-        <v>119.1959849731404</v>
+        <v>119.19598497314</v>
       </c>
       <c r="K44" t="n">
-        <v>304.9927226113313</v>
+        <v>489.4559849731461</v>
       </c>
       <c r="L44" t="n">
-        <v>535.4900049228892</v>
+        <v>719.9532672847039</v>
       </c>
       <c r="M44" t="n">
-        <v>535.4900049228892</v>
+        <v>719.953267284704</v>
       </c>
       <c r="N44" t="n">
-        <v>739.4315875548423</v>
+        <v>915.9847596412985</v>
       </c>
       <c r="O44" t="n">
-        <v>915.9847596413149</v>
+        <v>1286.244759641305</v>
       </c>
       <c r="P44" t="n">
-        <v>1125.740000000035</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="Q44" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="R44" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="S44" t="n">
-        <v>1326.072710052013</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="T44" t="n">
-        <v>1035.954407610592</v>
+        <v>1205.881697558605</v>
       </c>
       <c r="U44" t="n">
-        <v>1035.954407610592</v>
+        <v>846.1814284698603</v>
       </c>
       <c r="V44" t="n">
-        <v>1035.954407610592</v>
+        <v>505.9278687053917</v>
       </c>
       <c r="W44" t="n">
-        <v>687.0923106601401</v>
+        <v>157.0657717549396</v>
       </c>
       <c r="X44" t="n">
-        <v>384.7874283766374</v>
+        <v>157.0657717549396</v>
       </c>
       <c r="Y44" t="n">
-        <v>253.3256809198049</v>
+        <v>157.0657717549396</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>315.6172324016853</v>
+        <v>318.0281146698156</v>
       </c>
       <c r="C45" t="n">
-        <v>246.8294420526759</v>
+        <v>249.2403243208062</v>
       </c>
       <c r="D45" t="n">
-        <v>191.3368290246934</v>
+        <v>193.7477112928237</v>
       </c>
       <c r="E45" t="n">
-        <v>141.1629934470039</v>
+        <v>143.5738757151342</v>
       </c>
       <c r="F45" t="n">
-        <v>94.05567795419896</v>
+        <v>96.46656022232928</v>
       </c>
       <c r="G45" t="n">
-        <v>61.78280962226738</v>
+        <v>64.1936918903977</v>
       </c>
       <c r="H45" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="I45" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="J45" t="n">
-        <v>227.7113459300169</v>
+        <v>227.7113459300164</v>
       </c>
       <c r="K45" t="n">
-        <v>543.0996394772305</v>
+        <v>543.0996394772301</v>
       </c>
       <c r="L45" t="n">
-        <v>599.9270509017589</v>
+        <v>599.9270509017584</v>
       </c>
       <c r="M45" t="n">
-        <v>884.0224426446182</v>
+        <v>851.5752611842013</v>
       </c>
       <c r="N45" t="n">
-        <v>1188.111259659716</v>
+        <v>1188.111259659694</v>
       </c>
       <c r="O45" t="n">
-        <v>1234.237999492804</v>
+        <v>1234.237999492782</v>
       </c>
       <c r="P45" t="n">
-        <v>1496.000000000047</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="Q45" t="n">
-        <v>1493.589117731895</v>
+        <v>1496.000000000025</v>
       </c>
       <c r="R45" t="n">
-        <v>1286.253778366617</v>
+        <v>1288.664660634748</v>
       </c>
       <c r="S45" t="n">
-        <v>1125.747403330894</v>
+        <v>1128.158285599024</v>
       </c>
       <c r="T45" t="n">
-        <v>1015.468671550291</v>
+        <v>1017.879553818422</v>
       </c>
       <c r="U45" t="n">
-        <v>907.2278374109754</v>
+        <v>909.6387196791057</v>
       </c>
       <c r="V45" t="n">
-        <v>784.4897897427733</v>
+        <v>786.9006720109036</v>
       </c>
       <c r="W45" t="n">
-        <v>643.7088373086031</v>
+        <v>646.1197195767334</v>
       </c>
       <c r="X45" t="n">
-        <v>515.5646560506358</v>
+        <v>517.9755383187661</v>
       </c>
       <c r="Y45" t="n">
-        <v>408.0986027515102</v>
+        <v>410.5094850196405</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>470.7817775581353</v>
+        <v>470.7817775581349</v>
       </c>
       <c r="C46" t="n">
-        <v>490.8537833765711</v>
+        <v>490.8537833765707</v>
       </c>
       <c r="D46" t="n">
-        <v>498.2429275015712</v>
+        <v>498.2429275015708</v>
       </c>
       <c r="E46" t="n">
-        <v>510.1418317129842</v>
+        <v>510.1418317129838</v>
       </c>
       <c r="F46" t="n">
-        <v>528.5728043049197</v>
+        <v>528.5728043049193</v>
       </c>
       <c r="G46" t="n">
-        <v>576.7045554377066</v>
+        <v>576.7045554377062</v>
       </c>
       <c r="H46" t="n">
-        <v>646.1163330561205</v>
+        <v>646.1163330561201</v>
       </c>
       <c r="I46" t="n">
-        <v>781.0224192053182</v>
+        <v>781.0224192053178</v>
       </c>
       <c r="J46" t="n">
-        <v>1082.497756743016</v>
+        <v>1082.497756743015</v>
       </c>
       <c r="K46" t="n">
         <v>1163.052803794638</v>
       </c>
       <c r="L46" t="n">
-        <v>1130.572470666231</v>
+        <v>1163.052803794638</v>
       </c>
       <c r="M46" t="n">
-        <v>1005.430107765824</v>
+        <v>1037.910440894231</v>
       </c>
       <c r="N46" t="n">
-        <v>826.7320022587406</v>
+        <v>859.2123353871476</v>
       </c>
       <c r="O46" t="n">
-        <v>570.2646499020605</v>
+        <v>602.7449830304674</v>
       </c>
       <c r="P46" t="n">
-        <v>252.6830347832505</v>
+        <v>285.1633679116575</v>
       </c>
       <c r="Q46" t="n">
-        <v>252.6830347832505</v>
+        <v>88.34429643772498</v>
       </c>
       <c r="R46" t="n">
-        <v>88.34429643772542</v>
+        <v>88.34429643772498</v>
       </c>
       <c r="S46" t="n">
-        <v>29.92000000000094</v>
+        <v>29.9200000000005</v>
       </c>
       <c r="T46" t="n">
-        <v>114.8651070276583</v>
+        <v>114.8651070276578</v>
       </c>
       <c r="U46" t="n">
-        <v>255.522037042994</v>
+        <v>255.5220370429936</v>
       </c>
       <c r="V46" t="n">
-        <v>348.41342992894</v>
+        <v>348.4134299289396</v>
       </c>
       <c r="W46" t="n">
-        <v>414.3743481886174</v>
+        <v>414.374348188617</v>
       </c>
       <c r="X46" t="n">
-        <v>459.475139212811</v>
+        <v>459.4751392128105</v>
       </c>
       <c r="Y46" t="n">
-        <v>464.9544398918432</v>
+        <v>464.9544398918428</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,13 +7973,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>714.2808456769349</v>
+        <v>472.2608914614128</v>
       </c>
       <c r="N2" t="n">
         <v>404.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>375.1590153027356</v>
+        <v>243.1789695182578</v>
       </c>
       <c r="P2" t="n">
         <v>315.3213213472141</v>
@@ -8204,7 +8204,7 @@
         <v>374.2405037325275</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8213,7 +8213,7 @@
         <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>639.5838718235262</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>311.8831458198699</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="M8" t="n">
         <v>846.2608914614127</v>
       </c>
       <c r="N8" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>364.0430754681111</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8684,10 +8684,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>940.1988562855336</v>
+        <v>425.21565532575</v>
       </c>
       <c r="N11" t="n">
-        <v>354.0105711804039</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8915,25 +8915,25 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>467.326527638191</v>
+        <v>191.4566439443637</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>422.1744623115578</v>
       </c>
       <c r="M14" t="n">
-        <v>940.1988562855336</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N14" t="n">
-        <v>784.3153077665602</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>476.6634625389166</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,16 +9152,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>467.3265276381908</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>192.6633045704907</v>
       </c>
       <c r="M17" t="n">
-        <v>940.1988562855336</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N17" t="n">
-        <v>218.983604348868</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>467.326527638191</v>
+        <v>467.3265276381908</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>940.1988562855336</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N20" t="n">
-        <v>784.3153077666195</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>476.6634625389166</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>318.3533365013003</v>
       </c>
       <c r="Q20" t="n">
         <v>13.49857879984722</v>
@@ -9635,16 +9635,16 @@
         <v>285.1988562855334</v>
       </c>
       <c r="N23" t="n">
-        <v>540.4773829160841</v>
+        <v>414.7873509852764</v>
       </c>
       <c r="O23" t="n">
-        <v>476.6634625389185</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>467.3265276381971</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>422.1744623115642</v>
       </c>
       <c r="M26" t="n">
-        <v>940.1988562855395</v>
+        <v>940.1988562855393</v>
       </c>
       <c r="N26" t="n">
-        <v>218.9836043488893</v>
+        <v>362.140845455009</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,25 +10100,25 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>467.3265276381971</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>940.1988562855447</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N29" t="n">
-        <v>868.9937721401984</v>
+        <v>836.9618132968526</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>382.6480632645882</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,16 +10337,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>382.6480632645818</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>382.6480632645528</v>
       </c>
       <c r="M32" t="n">
-        <v>940.1988562855481</v>
+        <v>940.1988562855518</v>
       </c>
       <c r="N32" t="n">
-        <v>868.9937721402016</v>
+        <v>868.9937721402052</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10580,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>491.2004549036449</v>
+        <v>491.2004549036142</v>
       </c>
       <c r="N35" t="n">
-        <v>213.993772140187</v>
+        <v>587.9937721402307</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>387.4985787998819</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10653,19 +10653,19 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K36" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>222.6630187574459</v>
       </c>
       <c r="M36" t="n">
-        <v>471.6948204301074</v>
+        <v>184.7297782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>452.6335964032744</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>327.4073335019747</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10811,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>186.3265276381972</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>491.2004549036249</v>
+        <v>304.8739272653897</v>
       </c>
       <c r="N38" t="n">
-        <v>587.9937721402416</v>
+        <v>587.993772140258</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10887,13 +10887,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>65.71485604257725</v>
+        <v>27.675503614641</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>316.5985743187129</v>
+        <v>316.5985743187293</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -10902,10 +10902,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>327.4073335019856</v>
+        <v>146.2959740893342</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>283.822237400942</v>
+        <v>283.8222374009784</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -11054,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>581.3782175027375</v>
+        <v>581.3782175026797</v>
       </c>
       <c r="N41" t="n">
         <v>213.993772140187</v>
@@ -11133,7 +11133,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>438.9198896620317</v>
+        <v>438.9198896620101</v>
       </c>
       <c r="N42" t="n">
         <v>485.4085271713503</v>
@@ -11285,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>186.3265276381972</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -11294,16 +11294,16 @@
         <v>285.1988562855334</v>
       </c>
       <c r="N44" t="n">
-        <v>419.9953707583214</v>
+        <v>412.0053805811916</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>195.6634625389228</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>387.4985787998589</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11370,10 +11370,10 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>471.6948204301074</v>
+        <v>438.9198896620101</v>
       </c>
       <c r="N45" t="n">
-        <v>452.6335964032744</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -23277,7 +23277,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.6960849964949603</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -23286,7 +23286,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6960849964949034</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2.850361477466563</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23426,7 +23426,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.850361477466379</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -23475,61 +23475,61 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
         <v>0.696084996494875</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.696084996495216</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23937,7 +23937,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.696084996495216</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24131,7 +24131,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.850361477466322</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.85036147746635</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6960849964948983</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.696084996495216</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85036147746635</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6960849964683666</v>
+        <v>0.6960849964706546</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24614,10 +24614,10 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.850361477465924</v>
       </c>
       <c r="S28" t="n">
-        <v>2.850361477465931</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.6960849964706546</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6960849964497129</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24833,10 +24833,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.850361477466112</v>
       </c>
       <c r="M31" t="n">
-        <v>2.850361477466294</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.6960849963940774</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24939,7 +24939,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0.696084996449656</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.850361477454644</v>
+        <v>2.850361477460968</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25128,10 +25128,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>3.300929810531349</v>
       </c>
       <c r="F35" t="n">
-        <v>3.300929810510174</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -25368,7 +25368,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>3.300929810510174</v>
+        <v>3.300929810531326</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -25599,7 +25599,7 @@
         <v>156.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>117.3391557398498</v>
+        <v>102.8714258138249</v>
       </c>
       <c r="E41" t="n">
         <v>111.3632896068686</v>
@@ -25611,7 +25611,7 @@
         <v>109.2819954025941</v>
       </c>
       <c r="H41" t="n">
-        <v>99.89995518593948</v>
+        <v>99.89995518593946</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,13 +25644,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>173.407519423257</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25781,28 +25781,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>32.15552979712344</v>
+        <v>32.15552979712345</v>
       </c>
       <c r="M43" t="n">
         <v>123.8909392714024</v>
       </c>
       <c r="N43" t="n">
-        <v>114.852381001928</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>194.5070020442628</v>
       </c>
       <c r="P43" t="n">
-        <v>314.4057989676218</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.422266425525123</v>
+        <v>3.422266425488715</v>
       </c>
       <c r="R43" t="n">
-        <v>29.84504601386508</v>
+        <v>29.84504601382872</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>57.84005347334727</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>188.9993129555745</v>
+        <v>63.12499891818482</v>
       </c>
       <c r="C44" t="n">
         <v>156.4745782429939</v>
@@ -25842,10 +25842,10 @@
         <v>111.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>109.2819954025941</v>
       </c>
       <c r="H44" t="n">
         <v>99.89995518593948</v>
@@ -25881,25 +25881,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>356.1032663978569</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>336.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>88.17030270054229</v>
+        <v>218.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -26018,7 +26018,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>32.15552979712344</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -26033,10 +26033,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>377.422266425598</v>
+        <v>182.5713856664048</v>
       </c>
       <c r="R46" t="n">
-        <v>241.1496950518681</v>
+        <v>403.845046013938</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7588446.086065989</v>
+        <v>7588446.086065988</v>
       </c>
     </row>
     <row r="9">
@@ -26284,7 +26284,7 @@
         <v>1133327.900962275</v>
       </c>
       <c r="G2" t="n">
-        <v>1133327.900962274</v>
+        <v>1133327.900962275</v>
       </c>
       <c r="H2" t="n">
         <v>1133327.900962275</v>
@@ -26296,22 +26296,22 @@
         <v>1133327.900962276</v>
       </c>
       <c r="K2" t="n">
-        <v>1133327.900962278</v>
+        <v>1133327.900962276</v>
       </c>
       <c r="L2" t="n">
-        <v>1133327.900962278</v>
+        <v>1133327.900962282</v>
       </c>
       <c r="M2" t="n">
-        <v>1133202.85768771</v>
+        <v>1133202.857687708</v>
       </c>
       <c r="N2" t="n">
-        <v>1133202.85768771</v>
+        <v>1133202.857687708</v>
       </c>
       <c r="O2" t="n">
-        <v>1015827.590530277</v>
+        <v>1015827.590530276</v>
       </c>
       <c r="P2" t="n">
-        <v>1015827.590530277</v>
+        <v>1015827.590530275</v>
       </c>
     </row>
     <row r="3">
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>386848.0000000042</v>
+        <v>386848.0000000022</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101187</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.291951591</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685807</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687437</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731232</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963689981</v>
+        <v>503256.5379432672</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.0730285004</v>
+        <v>501580.9146027683</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045224</v>
+        <v>499902.9383787902</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.750526551</v>
+        <v>498222.5921008184</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963767</v>
+        <v>496539.8583706472</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842154</v>
+        <v>522371.0444804647</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.3308731503</v>
+        <v>520403.9137693994</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155939</v>
+        <v>447670.9673118431</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523485</v>
+        <v>446003.2126485977</v>
       </c>
     </row>
     <row r="5">
@@ -26449,25 +26449,25 @@
         <v>74642.611</v>
       </c>
       <c r="J5" t="n">
-        <v>74642.61100000072</v>
+        <v>74642.61100000038</v>
       </c>
       <c r="K5" t="n">
-        <v>74642.61100000072</v>
+        <v>74642.61100000038</v>
       </c>
       <c r="L5" t="n">
-        <v>74642.61100000072</v>
+        <v>74642.61100000038</v>
       </c>
       <c r="M5" t="n">
-        <v>64115.19300000071</v>
+        <v>64115.19300000038</v>
       </c>
       <c r="N5" t="n">
-        <v>64115.19300000071</v>
+        <v>64115.19300000038</v>
       </c>
       <c r="O5" t="n">
-        <v>55372.01700000071</v>
+        <v>55372.01700000039</v>
       </c>
       <c r="P5" t="n">
-        <v>55372.01700000071</v>
+        <v>55372.01700000039</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>241331.7600892162</v>
+        <v>241531.0747444312</v>
       </c>
       <c r="C6" t="n">
-        <v>474438.6822767052</v>
+        <v>474637.9969319199</v>
       </c>
       <c r="D6" t="n">
-        <v>476450.3296925292</v>
+        <v>476649.6443477438</v>
       </c>
       <c r="E6" t="n">
-        <v>-62265.32750630644</v>
+        <v>-62071.1690805745</v>
       </c>
       <c r="F6" t="n">
-        <v>551890.337993531</v>
+        <v>552084.496419263</v>
       </c>
       <c r="G6" t="n">
-        <v>553561.3061891508</v>
+        <v>553755.4646148836</v>
       </c>
       <c r="H6" t="n">
-        <v>555234.5935932763</v>
+        <v>555428.7520190072</v>
       </c>
       <c r="I6" t="n">
-        <v>556910.2169337741</v>
+        <v>557104.3753595062</v>
       </c>
       <c r="J6" t="n">
-        <v>171740.1931577483</v>
+        <v>171934.3515834829</v>
       </c>
       <c r="K6" t="n">
-        <v>560268.5394357258</v>
+        <v>560462.6978614571</v>
       </c>
       <c r="L6" t="n">
-        <v>561951.2731659004</v>
+        <v>562145.4315916342</v>
       </c>
       <c r="M6" t="n">
-        <v>484197.2031034937</v>
+        <v>484316.6202072434</v>
       </c>
       <c r="N6" t="n">
-        <v>548564.3338145587</v>
+        <v>548683.7509183078</v>
       </c>
       <c r="O6" t="n">
-        <v>340665.189114682</v>
+        <v>340784.6062184324</v>
       </c>
       <c r="P6" t="n">
-        <v>514332.9437779274</v>
+        <v>514452.3608816765</v>
       </c>
     </row>
   </sheetData>
@@ -26883,25 +26883,25 @@
         <v>655</v>
       </c>
       <c r="J4" t="n">
-        <v>655.0000000000117</v>
+        <v>655.0000000000063</v>
       </c>
       <c r="K4" t="n">
-        <v>655.0000000000117</v>
+        <v>655.0000000000063</v>
       </c>
       <c r="L4" t="n">
-        <v>655.0000000000117</v>
+        <v>655.0000000000063</v>
       </c>
       <c r="M4" t="n">
-        <v>374.0000000000117</v>
+        <v>374.0000000000063</v>
       </c>
       <c r="N4" t="n">
-        <v>374.0000000000117</v>
+        <v>374.0000000000063</v>
       </c>
       <c r="O4" t="n">
-        <v>374.0000000000117</v>
+        <v>374.0000000000063</v>
       </c>
       <c r="P4" t="n">
-        <v>374.0000000000117</v>
+        <v>374.0000000000063</v>
       </c>
     </row>
   </sheetData>
@@ -26990,7 +26990,7 @@
         <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -27008,7 +27008,7 @@
         <v>78</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>215</v>
@@ -27094,13 +27094,13 @@
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374.0000000000047</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27518,22 +27518,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>200.2217829794704</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.10257280615369</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27594,10 +27594,10 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27606,22 +27606,22 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
         <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
-        <v>22.26478490148153</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27645,19 +27645,19 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T4" t="n">
-        <v>375.9423166817565</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>164.5738043351572</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X4" t="n">
         <v>400</v>
-      </c>
-      <c r="X4" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27767,10 +27767,10 @@
         <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,13 +27797,13 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>375.4798020188998</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>88.48881128536601</v>
+        <v>302.1027491020745</v>
       </c>
       <c r="T6" t="n">
-        <v>30.47344446279683</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27815,10 +27815,10 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="7">
@@ -27849,16 +27849,16 @@
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>349.2746269966815</v>
       </c>
       <c r="J7" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27894,10 +27894,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>365.1835146730373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>57.98703223056765</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -27995,10 +27995,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>210.6652859026075</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.5201396486123</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28065,37 +28065,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>304.6227066913277</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>244.8599384153005</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J10" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28125,16 +28125,16 @@
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>337.1145144207066</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28223,13 +28223,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C12" t="n">
         <v>319</v>
       </c>
       <c r="D12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>319</v>
@@ -28238,13 +28238,13 @@
         <v>319</v>
       </c>
       <c r="G12" t="n">
-        <v>96.05772723972467</v>
+        <v>319</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,13 +28268,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.31352924142297</v>
+        <v>39.31886878759014</v>
       </c>
       <c r="R12" t="n">
         <v>319</v>
       </c>
       <c r="S12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>319</v>
@@ -28283,7 +28283,7 @@
         <v>319</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W12" t="n">
         <v>319</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C15" t="n">
         <v>319</v>
@@ -28472,7 +28472,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G15" t="n">
         <v>319</v>
@@ -28508,16 +28508,16 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R15" t="n">
-        <v>319</v>
+        <v>96.05772723972439</v>
       </c>
       <c r="S15" t="n">
         <v>319</v>
       </c>
       <c r="T15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>319</v>
@@ -28529,7 +28529,7 @@
         <v>319</v>
       </c>
       <c r="Y15" t="n">
-        <v>96.05772723972444</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16">
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>96.0577272397245</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -28706,7 +28706,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F18" t="n">
         <v>319</v>
@@ -28745,7 +28745,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R18" t="n">
-        <v>319</v>
+        <v>96.05772723972439</v>
       </c>
       <c r="S18" t="n">
         <v>319</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>158.2009556121548</v>
+        <v>158.200955612214</v>
       </c>
       <c r="S20" t="n">
         <v>319</v>
@@ -28934,19 +28934,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C21" t="n">
         <v>319</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>96.05772723972439</v>
       </c>
       <c r="F21" t="n">
-        <v>96.05772723972453</v>
+        <v>319</v>
       </c>
       <c r="G21" t="n">
         <v>319</v>
@@ -28991,13 +28991,13 @@
         <v>319</v>
       </c>
       <c r="U21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>319</v>
@@ -29171,10 +29171,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>319</v>
@@ -29189,10 +29189,10 @@
         <v>319</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="I24" t="n">
-        <v>39.31886878759042</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R24" t="n">
         <v>319</v>
@@ -29228,19 +29228,19 @@
         <v>319</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W24" t="n">
         <v>319</v>
       </c>
       <c r="X24" t="n">
-        <v>319</v>
+        <v>96.05772723972456</v>
       </c>
       <c r="Y24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29408,16 +29408,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>96.0577272397245</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>96.05772723972456</v>
+        <v>319</v>
       </c>
       <c r="E27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -29651,22 +29651,22 @@
         <v>319</v>
       </c>
       <c r="D30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G30" t="n">
-        <v>319</v>
+        <v>286.0053395461675</v>
       </c>
       <c r="H30" t="n">
-        <v>96.05772723972424</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29705,10 +29705,10 @@
         <v>319</v>
       </c>
       <c r="V30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X30" t="n">
         <v>319</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>158.200955612214</v>
+        <v>158.2009556122906</v>
       </c>
       <c r="S32" t="n">
         <v>319</v>
@@ -29882,28 +29882,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>319</v>
+        <v>286.0053395461675</v>
       </c>
       <c r="C33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>319</v>
       </c>
       <c r="G33" t="n">
-        <v>168.3712564811475</v>
+        <v>319</v>
       </c>
       <c r="H33" t="n">
         <v>319</v>
       </c>
       <c r="I33" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R33" t="n">
         <v>319</v>
@@ -29939,10 +29939,10 @@
         <v>319</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W33" t="n">
         <v>319</v>
@@ -29951,7 +29951,7 @@
         <v>319</v>
       </c>
       <c r="Y33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -29964,7 +29964,7 @@
         <v>319</v>
       </c>
       <c r="C34" t="n">
-        <v>319.0000000000121</v>
+        <v>319</v>
       </c>
       <c r="D34" t="n">
         <v>319</v>
@@ -29985,7 +29985,7 @@
         <v>319</v>
       </c>
       <c r="J34" t="n">
-        <v>319</v>
+        <v>319.0000000000053</v>
       </c>
       <c r="K34" t="n">
         <v>319</v>
@@ -30119,16 +30119,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10.55655664629197</v>
+        <v>10.55655664628287</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>58.93603180444467</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -30137,7 +30137,7 @@
         <v>324.9501396486123</v>
       </c>
       <c r="H36" t="n">
-        <v>324.5441815260438</v>
+        <v>123.6303401384189</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>397</v>
@@ -30188,7 +30188,7 @@
         <v>397</v>
       </c>
       <c r="Y36" t="n">
-        <v>397</v>
+        <v>25.39139276609066</v>
       </c>
     </row>
     <row r="37">
@@ -30201,16 +30201,16 @@
         <v>397</v>
       </c>
       <c r="C37" t="n">
-        <v>272.7252466480447</v>
+        <v>397</v>
       </c>
       <c r="D37" t="n">
         <v>397</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>397</v>
       </c>
       <c r="F37" t="n">
-        <v>274.3828559677419</v>
+        <v>397</v>
       </c>
       <c r="G37" t="n">
         <v>244.3820695628415</v>
@@ -30252,22 +30252,22 @@
         <v>350.8400534733473</v>
       </c>
       <c r="T37" t="n">
-        <v>393.9959372005359</v>
+        <v>397</v>
       </c>
       <c r="U37" t="n">
-        <v>150.9222929138022</v>
+        <v>214.7254294488016</v>
       </c>
       <c r="V37" t="n">
         <v>397</v>
       </c>
       <c r="W37" t="n">
-        <v>397</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>397</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
-        <v>397</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="38">
@@ -30359,13 +30359,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>254.8758779749694</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R39" t="n">
         <v>397</v>
@@ -30422,7 +30422,7 @@
         <v>397</v>
       </c>
       <c r="X39" t="n">
-        <v>397</v>
+        <v>236.8902515116552</v>
       </c>
       <c r="Y39" t="n">
         <v>397</v>
@@ -30456,7 +30456,7 @@
         <v>222.8870933147334</v>
       </c>
       <c r="I40" t="n">
-        <v>377.2099039379908</v>
+        <v>156.7312261119215</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -30486,19 +30486,19 @@
         <v>397</v>
       </c>
       <c r="S40" t="n">
-        <v>350.8400534733473</v>
+        <v>392.6649897661175</v>
       </c>
       <c r="T40" t="n">
-        <v>397</v>
+        <v>207.1968615882249</v>
       </c>
       <c r="U40" t="n">
         <v>150.9222929138022</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>397</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>397</v>
       </c>
       <c r="X40" t="n">
         <v>247.4436454301076</v>
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>293</v>
+        <v>290.6132265545506</v>
       </c>
       <c r="C42" t="n">
         <v>293</v>
@@ -30605,7 +30605,7 @@
         <v>293</v>
       </c>
       <c r="F42" t="n">
-        <v>290.6132265545294</v>
+        <v>293</v>
       </c>
       <c r="G42" t="n">
         <v>293</v>
@@ -30848,7 +30848,7 @@
         <v>293</v>
       </c>
       <c r="H45" t="n">
-        <v>293</v>
+        <v>290.6132265545505</v>
       </c>
       <c r="I45" t="n">
         <v>189.9476123064429</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>69.92675579595237</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R45" t="n">
         <v>293</v>
@@ -34743,22 +34743,22 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512562</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>242.0199542155221</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>374</v>
       </c>
       <c r="P2" t="n">
         <v>374</v>
@@ -34880,10 +34880,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34892,22 +34892,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34931,19 +34931,19 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>166.703651814843</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>13.62544584758449</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34983,7 +34983,7 @@
         <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>373.9999999999999</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L5" t="n">
         <v>64.70900502512563</v>
@@ -34992,7 +34992,7 @@
         <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>235.5012052109774</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35001,7 +35001,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35135,16 +35135,16 @@
         <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>178.1725812126288</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35180,10 +35180,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>77.71816182357487</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>373.9999999999999</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>248.0502805878618</v>
       </c>
       <c r="M8" t="n">
         <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>235.5012052109774</v>
+        <v>374</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,37 +35351,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>19.08648863577226</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35411,16 +35411,16 @@
         <v>249.0516415124273</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>137.9442042044904</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35463,10 +35463,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M11" t="n">
+        <v>140.0167990402167</v>
+      </c>
+      <c r="N11" t="n">
         <v>655.0000000000001</v>
-      </c>
-      <c r="N11" t="n">
-        <v>140.0167990402169</v>
       </c>
       <c r="O11" t="n">
         <v>178.3365374610834</v>
@@ -35694,25 +35694,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K14" t="n">
+        <v>379.1301163061727</v>
+      </c>
+      <c r="L14" t="n">
         <v>655</v>
       </c>
-      <c r="L14" t="n">
-        <v>232.8255376884423</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>655.0000000000001</v>
-      </c>
-      <c r="N14" t="n">
-        <v>570.3215356263732</v>
-      </c>
-      <c r="O14" t="n">
-        <v>178.3365374610834</v>
       </c>
       <c r="P14" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35931,16 +35931,16 @@
         <v>520.4824991852875</v>
       </c>
       <c r="K17" t="n">
-        <v>187.6734723618091</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>232.8255376884422</v>
+        <v>425.4888422589329</v>
       </c>
       <c r="M17" t="n">
-        <v>655.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.989832208681</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>178.3365374610834</v>
@@ -36165,31 +36165,31 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K20" t="n">
-        <v>655</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>655.0000000000001</v>
       </c>
-      <c r="N20" t="n">
-        <v>570.3215356264325</v>
-      </c>
-      <c r="O20" t="n">
-        <v>178.3365374610834</v>
-      </c>
       <c r="P20" t="n">
-        <v>211.8739801603236</v>
+        <v>530.2273166616239</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-5.925495784278169e-11</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36326,7 +36326,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K22" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36414,16 +36414,16 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>326.4836107758971</v>
+        <v>200.7935788450894</v>
       </c>
       <c r="O23" t="n">
-        <v>655.0000000000019</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P23" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36563,7 +36563,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K25" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K26" t="n">
-        <v>187.6734723618091</v>
+        <v>655.0000000000063</v>
       </c>
       <c r="L26" t="n">
-        <v>232.8255376884422</v>
+        <v>655.0000000000064</v>
       </c>
       <c r="M26" t="n">
-        <v>655.000000000006</v>
+        <v>655.0000000000058</v>
       </c>
       <c r="N26" t="n">
-        <v>4.989832208702359</v>
+        <v>148.147073314822</v>
       </c>
       <c r="O26" t="n">
         <v>178.3365374610834</v>
@@ -36660,7 +36660,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q26" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36879,25 +36879,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K29" t="n">
-        <v>187.6734723618091</v>
+        <v>655.0000000000063</v>
       </c>
       <c r="L29" t="n">
         <v>232.8255376884422</v>
       </c>
       <c r="M29" t="n">
-        <v>655.0000000000113</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>655.0000000000113</v>
+        <v>622.9680411566655</v>
       </c>
       <c r="O29" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P29" t="n">
-        <v>594.5220434249119</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37116,16 +37116,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K32" t="n">
-        <v>570.3215356263908</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L32" t="n">
-        <v>232.8255376884422</v>
+        <v>615.473600952995</v>
       </c>
       <c r="M32" t="n">
-        <v>655.0000000000147</v>
+        <v>655.0000000000183</v>
       </c>
       <c r="N32" t="n">
-        <v>655.0000000000147</v>
+        <v>655.0000000000183</v>
       </c>
       <c r="O32" t="n">
         <v>178.3365374610834</v>
@@ -37250,7 +37250,7 @@
         <v>31.88619966292134</v>
       </c>
       <c r="C34" t="n">
-        <v>46.27475335196743</v>
+        <v>46.27475335195533</v>
       </c>
       <c r="D34" t="n">
         <v>33.46378194444452</v>
@@ -37271,7 +37271,7 @@
         <v>162.2687738880785</v>
       </c>
       <c r="J34" t="n">
-        <v>330.5205429673709</v>
+        <v>330.5205429673762</v>
       </c>
       <c r="K34" t="n">
         <v>107.3687343955783</v>
@@ -37356,13 +37356,13 @@
         <v>187.673472361809</v>
       </c>
       <c r="L35" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M35" t="n">
-        <v>206.0015986181115</v>
+        <v>206.0015986180808</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>374.0000000000437</v>
       </c>
       <c r="O35" t="n">
         <v>178.3365374610834</v>
@@ -37371,7 +37371,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q35" t="n">
-        <v>374.0000000000346</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37432,19 +37432,19 @@
         <v>199.7892383131474</v>
       </c>
       <c r="K36" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L36" t="n">
-        <v>57.40142568134173</v>
+        <v>280.0644444387876</v>
       </c>
       <c r="M36" t="n">
-        <v>286.9650421645043</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>307.1604212273714</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O36" t="n">
-        <v>46.59266649806909</v>
+        <v>374.0000000000437</v>
       </c>
       <c r="P36" t="n">
         <v>264.4060611184268</v>
@@ -37487,16 +37487,16 @@
         <v>109.8861996629213</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>124.2747533519553</v>
       </c>
       <c r="D37" t="n">
         <v>111.4637819444445</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>116.0190951630435</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -37538,22 +37538,22 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>186.7990756123109</v>
+        <v>189.8031384117751</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>63.80313653499936</v>
       </c>
       <c r="V37" t="n">
         <v>197.8296897837838</v>
       </c>
       <c r="W37" t="n">
-        <v>170.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>149.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>109.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -37590,16 +37590,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K38" t="n">
-        <v>187.673472361809</v>
+        <v>374.0000000000063</v>
       </c>
       <c r="L38" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M38" t="n">
-        <v>206.0015986180915</v>
+        <v>19.67507097985636</v>
       </c>
       <c r="N38" t="n">
-        <v>374.0000000000546</v>
+        <v>374.000000000071</v>
       </c>
       <c r="O38" t="n">
         <v>178.3365374610834</v>
@@ -37666,13 +37666,13 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>38.03935242793624</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>22.69379302306083</v>
       </c>
       <c r="L39" t="n">
-        <v>374.0000000000546</v>
+        <v>374.000000000071</v>
       </c>
       <c r="M39" t="n">
         <v>286.9650421645043</v>
@@ -37681,10 +37681,10 @@
         <v>339.9353519954473</v>
       </c>
       <c r="O39" t="n">
-        <v>374.0000000000546</v>
+        <v>192.8886405874032</v>
       </c>
       <c r="P39" t="n">
-        <v>45.25534927787736</v>
+        <v>264.4060611184268</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37742,7 +37742,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>220.4786778260692</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>11.52054296737091</v>
@@ -37772,19 +37772,19 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>41.82493629277023</v>
       </c>
       <c r="T40" t="n">
-        <v>189.8031384117751</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>197.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>170.6271901612903</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -37824,16 +37824,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>374.0000000000728</v>
+        <v>374.0000000001092</v>
       </c>
       <c r="K41" t="n">
-        <v>187.6734723618091</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L41" t="n">
         <v>232.8255376884422</v>
       </c>
       <c r="M41" t="n">
-        <v>296.1793612172041</v>
+        <v>296.1793612171462</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -37912,7 +37912,7 @@
         <v>57.40142568134173</v>
       </c>
       <c r="M42" t="n">
-        <v>254.1901113964285</v>
+        <v>254.1901113964069</v>
       </c>
       <c r="N42" t="n">
         <v>339.9353519954473</v>
@@ -37979,13 +37979,13 @@
         <v>70.11290668526664</v>
       </c>
       <c r="I43" t="n">
-        <v>136.2687738880784</v>
+        <v>136.2687738880785</v>
       </c>
       <c r="J43" t="n">
         <v>304.5205429673709</v>
       </c>
       <c r="K43" t="n">
-        <v>81.36873439557824</v>
+        <v>81.36873439557826</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>85.80313841177507</v>
+        <v>85.80313841177508</v>
       </c>
       <c r="U43" t="n">
         <v>142.0777070861978</v>
@@ -38064,25 +38064,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K44" t="n">
-        <v>187.673472361809</v>
+        <v>374.0000000000063</v>
       </c>
       <c r="L44" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>206.0015986181345</v>
+        <v>198.0116084410046</v>
       </c>
       <c r="O44" t="n">
-        <v>178.3365374610834</v>
+        <v>374.0000000000063</v>
       </c>
       <c r="P44" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q44" t="n">
-        <v>374.0000000000117</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38149,10 +38149,10 @@
         <v>57.40142568134173</v>
       </c>
       <c r="M45" t="n">
-        <v>286.9650421645043</v>
+        <v>254.1901113964069</v>
       </c>
       <c r="N45" t="n">
-        <v>307.1604212273714</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O45" t="n">
         <v>46.59266649806909</v>
